--- a/Interview-Preparation-Tracker.xlsx
+++ b/Interview-Preparation-Tracker.xlsx
@@ -8,20 +8,21 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DSA Problems" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Java &amp; Backend" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Design" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kafka &amp; Redis" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cloud &amp; Platform" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mock Interviews" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Books &amp; Blogs" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applications" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revision Tracker" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pattern Mastery" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DSA Problems" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Java &amp; Backend" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Design" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kafka &amp; Redis" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cloud &amp; Platform" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mock Interviews" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Books &amp; Blogs" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applications" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revision Tracker" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DSA Problems'!$A$1:$S$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DSA Problems'!$A$1:$S$143</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -96,6 +97,35 @@
       <color rgb="00F87171"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="0094A3B8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0060A5FA"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="0094A3B8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0034D399"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FBBF24"/>
+      <sz val="14"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -130,7 +160,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -152,11 +182,44 @@
         <color rgb="002D3748"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="002D3748"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="002D3748"/>
+      </right>
+      <top style="thin">
+        <color rgb="002D3748"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="002D3748"/>
+      </right>
+      <top style="thin">
+        <color rgb="002D3748"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="002D3748"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -217,10 +280,77 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="0034D399"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="001A3A2A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="00FBBF24"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="003A3520"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="00F87171"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="003A1A1A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -1059,6 +1189,705 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FB923C"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Pattern</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Solved?</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Pattern</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Solved?</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Score(1-10)</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Mistakes</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Lessons</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+      <c r="P2" s="5" t="n"/>
+      <c r="Q2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="7" t="n"/>
+      <c r="I3" s="7" t="n"/>
+      <c r="J3" s="7" t="n"/>
+      <c r="K3" s="7" t="n"/>
+      <c r="L3" s="7" t="n"/>
+      <c r="M3" s="7" t="n"/>
+      <c r="N3" s="7" t="n"/>
+      <c r="O3" s="7" t="n"/>
+      <c r="P3" s="7" t="n"/>
+      <c r="Q3" s="7" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
+      <c r="Q4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="n"/>
+      <c r="L5" s="7" t="n"/>
+      <c r="M5" s="7" t="n"/>
+      <c r="N5" s="7" t="n"/>
+      <c r="O5" s="7" t="n"/>
+      <c r="P5" s="7" t="n"/>
+      <c r="Q5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="7" t="n"/>
+      <c r="L7" s="7" t="n"/>
+      <c r="M7" s="7" t="n"/>
+      <c r="N7" s="7" t="n"/>
+      <c r="O7" s="7" t="n"/>
+      <c r="P7" s="7" t="n"/>
+      <c r="Q7" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="M9" s="7" t="n"/>
+      <c r="N9" s="7" t="n"/>
+      <c r="O9" s="7" t="n"/>
+      <c r="P9" s="7" t="n"/>
+      <c r="Q9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
+      <c r="Q10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="7" t="n"/>
+      <c r="M11" s="7" t="n"/>
+      <c r="N11" s="7" t="n"/>
+      <c r="O11" s="7" t="n"/>
+      <c r="P11" s="7" t="n"/>
+      <c r="Q11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
+      <c r="Q12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="7" t="n"/>
+      <c r="M13" s="7" t="n"/>
+      <c r="N13" s="7" t="n"/>
+      <c r="O13" s="7" t="n"/>
+      <c r="P13" s="7" t="n"/>
+      <c r="Q13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
+      <c r="Q14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="7" t="n"/>
+      <c r="N15" s="7" t="n"/>
+      <c r="O15" s="7" t="n"/>
+      <c r="P15" s="7" t="n"/>
+      <c r="Q15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
+      <c r="Q16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="7" t="n"/>
+      <c r="K17" s="7" t="n"/>
+      <c r="L17" s="7" t="n"/>
+      <c r="M17" s="7" t="n"/>
+      <c r="N17" s="7" t="n"/>
+      <c r="O17" s="7" t="n"/>
+      <c r="P17" s="7" t="n"/>
+      <c r="Q17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
+      <c r="Q18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="7" t="n"/>
+      <c r="K19" s="7" t="n"/>
+      <c r="L19" s="7" t="n"/>
+      <c r="M19" s="7" t="n"/>
+      <c r="N19" s="7" t="n"/>
+      <c r="O19" s="7" t="n"/>
+      <c r="P19" s="7" t="n"/>
+      <c r="Q19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="7" t="n"/>
+      <c r="J21" s="7" t="n"/>
+      <c r="K21" s="7" t="n"/>
+      <c r="L21" s="7" t="n"/>
+      <c r="M21" s="7" t="n"/>
+      <c r="N21" s="7" t="n"/>
+      <c r="O21" s="7" t="n"/>
+      <c r="P21" s="7" t="n"/>
+      <c r="Q21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
+      <c r="Q22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="7" t="n"/>
+      <c r="J23" s="7" t="n"/>
+      <c r="K23" s="7" t="n"/>
+      <c r="L23" s="7" t="n"/>
+      <c r="M23" s="7" t="n"/>
+      <c r="N23" s="7" t="n"/>
+      <c r="O23" s="7" t="n"/>
+      <c r="P23" s="7" t="n"/>
+      <c r="Q23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
+      <c r="Q24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="7" t="n"/>
+      <c r="J25" s="7" t="n"/>
+      <c r="K25" s="7" t="n"/>
+      <c r="L25" s="7" t="n"/>
+      <c r="M25" s="7" t="n"/>
+      <c r="N25" s="7" t="n"/>
+      <c r="O25" s="7" t="n"/>
+      <c r="P25" s="7" t="n"/>
+      <c r="Q25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="5" t="n"/>
+      <c r="Q26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="7" t="n"/>
+      <c r="I27" s="7" t="n"/>
+      <c r="J27" s="7" t="n"/>
+      <c r="K27" s="7" t="n"/>
+      <c r="L27" s="7" t="n"/>
+      <c r="M27" s="7" t="n"/>
+      <c r="N27" s="7" t="n"/>
+      <c r="O27" s="7" t="n"/>
+      <c r="P27" s="7" t="n"/>
+      <c r="Q27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
+      <c r="Q28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="7" t="n"/>
+      <c r="I29" s="7" t="n"/>
+      <c r="J29" s="7" t="n"/>
+      <c r="K29" s="7" t="n"/>
+      <c r="L29" s="7" t="n"/>
+      <c r="M29" s="7" t="n"/>
+      <c r="N29" s="7" t="n"/>
+      <c r="O29" s="7" t="n"/>
+      <c r="P29" s="7" t="n"/>
+      <c r="Q29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+      <c r="P30" s="5" t="n"/>
+      <c r="Q30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="7" t="n"/>
+      <c r="I31" s="7" t="n"/>
+      <c r="J31" s="7" t="n"/>
+      <c r="K31" s="7" t="n"/>
+      <c r="L31" s="7" t="n"/>
+      <c r="M31" s="7" t="n"/>
+      <c r="N31" s="7" t="n"/>
+      <c r="O31" s="7" t="n"/>
+      <c r="P31" s="7" t="n"/>
+      <c r="Q31" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B2:B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Timed Solo,Peer Mock,Platform,Company Prep,System Design Mock"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"LeetCode,Pramp,Interviewing.io,Peer,Self,Hello Interview"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00FBBF24"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1595,7 +2424,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00F87171"/>
@@ -2455,7 +3284,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00FBBF24"/>
@@ -6096,6 +6925,5293 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00A78BFA"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J352"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PATTERN MASTERY — Interview Readiness Assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>"If an interviewer gives me a brand-new problem from this pattern, can I derive the optimal solution without memorization?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>STATISTICS DASHBOARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>Total Patterns</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="n">
+        <v>26</v>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>Interview Ready</t>
+        </is>
+      </c>
+      <c r="D5" s="25">
+        <f>COUNTIFS(C10:C35,"&gt;=4",H10:H35,"&gt;=4")</f>
+        <v/>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>Needs Revision</t>
+        </is>
+      </c>
+      <c r="F5" s="26">
+        <f>26-B5</f>
+        <v/>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>Avg Recognition</t>
+        </is>
+      </c>
+      <c r="H5" s="25">
+        <f>IF(COUNTA(C10:C35)&gt;0,ROUND(AVERAGE(C10:C35),1),"—")</f>
+        <v/>
+      </c>
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t>Avg Confidence</t>
+        </is>
+      </c>
+      <c r="J5" s="25">
+        <f>IF(COUNTA(H10:H35)&gt;0,ROUND(AVERAGE(H10:H35),1),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Strongest Pattern</t>
+        </is>
+      </c>
+      <c r="B6" s="18">
+        <f>IF(COUNTA(H10:H35)&gt;0,INDEX(A10:A35,MATCH(MAX(H10:H35),H10:H35,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="C6" s="28" t="n"/>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>Weakest Pattern</t>
+        </is>
+      </c>
+      <c r="E6" s="17">
+        <f>IF(COUNTA(H10:H35)&gt;0,INDEX(A10:A35,MATCH(MIN(H10:H35),H10:H35,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="27" t="inlineStr">
+        <is>
+          <t>Completion %</t>
+        </is>
+      </c>
+      <c r="H6" s="29">
+        <f>IF(COUNTA(H10:H35)&gt;0,ROUND(COUNTIF(H10:H35,"&gt;=4")/26*100,0)&amp;"%","0%")</f>
+        <v/>
+      </c>
+      <c r="I6" s="28" t="n"/>
+      <c r="J6" s="28" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>RECOGNITION SCALE: 1=Never recognize  2=Need hints  3=Recognize after thinking  4=Recognize quickly  5=Instantly       CONFIDENCE: 1=Cannot solve  2=Need help  3=Struggle  4=Independent  5=Interview ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Pattern</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Problems Solved</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Recognition (1-5)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Can Solve Without Hints</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Can Explain Intuition</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Can Explain Complexity</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Can Solve Variants</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Confidence (1-5)</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Weak Areas</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Arrays &amp; Hashing</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Prefix Sum</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Sliding Window</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Binary Search</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Bit Manipulation</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Stack</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Monotonic Stack</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Queue</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Heap / Priority Queue</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Linked List</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Fast &amp; Slow Pointer</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="7" t="n"/>
+      <c r="J21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Trees (DFS)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Trees (BFS)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="7" t="n"/>
+      <c r="J23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Binary Search Tree</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Graph DFS</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="7" t="n"/>
+      <c r="J25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Graph BFS</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Topological Sort</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="7" t="n"/>
+      <c r="I27" s="7" t="n"/>
+      <c r="J27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Union Find (Disjoint Set)</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Trie</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="7" t="n"/>
+      <c r="I29" s="7" t="n"/>
+      <c r="J29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Backtracking</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Greedy</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="7" t="n"/>
+      <c r="I31" s="7" t="n"/>
+      <c r="J31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Dynamic Programming</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Interval Problems</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="7" t="n"/>
+      <c r="I33" s="7" t="n"/>
+      <c r="J33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Matrix Problems</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Design Problems</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="7" t="n"/>
+      <c r="I35" s="7" t="n"/>
+      <c r="J35" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>INTERVIEW READINESS DECISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Pattern</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Recognition</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>No Hints?</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Explain?</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Variants?</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Arrays &amp; Hashing</t>
+        </is>
+      </c>
+      <c r="B39" s="5">
+        <f>C10</f>
+        <v/>
+      </c>
+      <c r="C39" s="5">
+        <f>H10</f>
+        <v/>
+      </c>
+      <c r="D39" s="5">
+        <f>D10</f>
+        <v/>
+      </c>
+      <c r="E39" s="5">
+        <f>E10</f>
+        <v/>
+      </c>
+      <c r="F39" s="5">
+        <f>G10</f>
+        <v/>
+      </c>
+      <c r="G39" s="5">
+        <f>IF(AND(C10&gt;=4,H10&gt;=4,D10="Yes",E10="Yes",G10="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Prefix Sum</t>
+        </is>
+      </c>
+      <c r="B40" s="7">
+        <f>C11</f>
+        <v/>
+      </c>
+      <c r="C40" s="7">
+        <f>H11</f>
+        <v/>
+      </c>
+      <c r="D40" s="7">
+        <f>D11</f>
+        <v/>
+      </c>
+      <c r="E40" s="7">
+        <f>E11</f>
+        <v/>
+      </c>
+      <c r="F40" s="7">
+        <f>G11</f>
+        <v/>
+      </c>
+      <c r="G40" s="7">
+        <f>IF(AND(C11&gt;=4,H11&gt;=4,D11="Yes",E11="Yes",G11="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="B41" s="5">
+        <f>C12</f>
+        <v/>
+      </c>
+      <c r="C41" s="5">
+        <f>H12</f>
+        <v/>
+      </c>
+      <c r="D41" s="5">
+        <f>D12</f>
+        <v/>
+      </c>
+      <c r="E41" s="5">
+        <f>E12</f>
+        <v/>
+      </c>
+      <c r="F41" s="5">
+        <f>G12</f>
+        <v/>
+      </c>
+      <c r="G41" s="5">
+        <f>IF(AND(C12&gt;=4,H12&gt;=4,D12="Yes",E12="Yes",G12="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Sliding Window</t>
+        </is>
+      </c>
+      <c r="B42" s="7">
+        <f>C13</f>
+        <v/>
+      </c>
+      <c r="C42" s="7">
+        <f>H13</f>
+        <v/>
+      </c>
+      <c r="D42" s="7">
+        <f>D13</f>
+        <v/>
+      </c>
+      <c r="E42" s="7">
+        <f>E13</f>
+        <v/>
+      </c>
+      <c r="F42" s="7">
+        <f>G13</f>
+        <v/>
+      </c>
+      <c r="G42" s="7">
+        <f>IF(AND(C13&gt;=4,H13&gt;=4,D13="Yes",E13="Yes",G13="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Binary Search</t>
+        </is>
+      </c>
+      <c r="B43" s="5">
+        <f>C14</f>
+        <v/>
+      </c>
+      <c r="C43" s="5">
+        <f>H14</f>
+        <v/>
+      </c>
+      <c r="D43" s="5">
+        <f>D14</f>
+        <v/>
+      </c>
+      <c r="E43" s="5">
+        <f>E14</f>
+        <v/>
+      </c>
+      <c r="F43" s="5">
+        <f>G14</f>
+        <v/>
+      </c>
+      <c r="G43" s="5">
+        <f>IF(AND(C14&gt;=4,H14&gt;=4,D14="Yes",E14="Yes",G14="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Bit Manipulation</t>
+        </is>
+      </c>
+      <c r="B44" s="7">
+        <f>C15</f>
+        <v/>
+      </c>
+      <c r="C44" s="7">
+        <f>H15</f>
+        <v/>
+      </c>
+      <c r="D44" s="7">
+        <f>D15</f>
+        <v/>
+      </c>
+      <c r="E44" s="7">
+        <f>E15</f>
+        <v/>
+      </c>
+      <c r="F44" s="7">
+        <f>G15</f>
+        <v/>
+      </c>
+      <c r="G44" s="7">
+        <f>IF(AND(C15&gt;=4,H15&gt;=4,D15="Yes",E15="Yes",G15="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Stack</t>
+        </is>
+      </c>
+      <c r="B45" s="5">
+        <f>C16</f>
+        <v/>
+      </c>
+      <c r="C45" s="5">
+        <f>H16</f>
+        <v/>
+      </c>
+      <c r="D45" s="5">
+        <f>D16</f>
+        <v/>
+      </c>
+      <c r="E45" s="5">
+        <f>E16</f>
+        <v/>
+      </c>
+      <c r="F45" s="5">
+        <f>G16</f>
+        <v/>
+      </c>
+      <c r="G45" s="5">
+        <f>IF(AND(C16&gt;=4,H16&gt;=4,D16="Yes",E16="Yes",G16="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Monotonic Stack</t>
+        </is>
+      </c>
+      <c r="B46" s="7">
+        <f>C17</f>
+        <v/>
+      </c>
+      <c r="C46" s="7">
+        <f>H17</f>
+        <v/>
+      </c>
+      <c r="D46" s="7">
+        <f>D17</f>
+        <v/>
+      </c>
+      <c r="E46" s="7">
+        <f>E17</f>
+        <v/>
+      </c>
+      <c r="F46" s="7">
+        <f>G17</f>
+        <v/>
+      </c>
+      <c r="G46" s="7">
+        <f>IF(AND(C17&gt;=4,H17&gt;=4,D17="Yes",E17="Yes",G17="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Queue</t>
+        </is>
+      </c>
+      <c r="B47" s="5">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="C47" s="5">
+        <f>H18</f>
+        <v/>
+      </c>
+      <c r="D47" s="5">
+        <f>D18</f>
+        <v/>
+      </c>
+      <c r="E47" s="5">
+        <f>E18</f>
+        <v/>
+      </c>
+      <c r="F47" s="5">
+        <f>G18</f>
+        <v/>
+      </c>
+      <c r="G47" s="5">
+        <f>IF(AND(C18&gt;=4,H18&gt;=4,D18="Yes",E18="Yes",G18="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Heap / Priority Queue</t>
+        </is>
+      </c>
+      <c r="B48" s="7">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="C48" s="7">
+        <f>H19</f>
+        <v/>
+      </c>
+      <c r="D48" s="7">
+        <f>D19</f>
+        <v/>
+      </c>
+      <c r="E48" s="7">
+        <f>E19</f>
+        <v/>
+      </c>
+      <c r="F48" s="7">
+        <f>G19</f>
+        <v/>
+      </c>
+      <c r="G48" s="7">
+        <f>IF(AND(C19&gt;=4,H19&gt;=4,D19="Yes",E19="Yes",G19="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Linked List</t>
+        </is>
+      </c>
+      <c r="B49" s="5">
+        <f>C20</f>
+        <v/>
+      </c>
+      <c r="C49" s="5">
+        <f>H20</f>
+        <v/>
+      </c>
+      <c r="D49" s="5">
+        <f>D20</f>
+        <v/>
+      </c>
+      <c r="E49" s="5">
+        <f>E20</f>
+        <v/>
+      </c>
+      <c r="F49" s="5">
+        <f>G20</f>
+        <v/>
+      </c>
+      <c r="G49" s="5">
+        <f>IF(AND(C20&gt;=4,H20&gt;=4,D20="Yes",E20="Yes",G20="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Fast &amp; Slow Pointer</t>
+        </is>
+      </c>
+      <c r="B50" s="7">
+        <f>C21</f>
+        <v/>
+      </c>
+      <c r="C50" s="7">
+        <f>H21</f>
+        <v/>
+      </c>
+      <c r="D50" s="7">
+        <f>D21</f>
+        <v/>
+      </c>
+      <c r="E50" s="7">
+        <f>E21</f>
+        <v/>
+      </c>
+      <c r="F50" s="7">
+        <f>G21</f>
+        <v/>
+      </c>
+      <c r="G50" s="7">
+        <f>IF(AND(C21&gt;=4,H21&gt;=4,D21="Yes",E21="Yes",G21="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Trees (DFS)</t>
+        </is>
+      </c>
+      <c r="B51" s="5">
+        <f>C22</f>
+        <v/>
+      </c>
+      <c r="C51" s="5">
+        <f>H22</f>
+        <v/>
+      </c>
+      <c r="D51" s="5">
+        <f>D22</f>
+        <v/>
+      </c>
+      <c r="E51" s="5">
+        <f>E22</f>
+        <v/>
+      </c>
+      <c r="F51" s="5">
+        <f>G22</f>
+        <v/>
+      </c>
+      <c r="G51" s="5">
+        <f>IF(AND(C22&gt;=4,H22&gt;=4,D22="Yes",E22="Yes",G22="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Trees (BFS)</t>
+        </is>
+      </c>
+      <c r="B52" s="7">
+        <f>C23</f>
+        <v/>
+      </c>
+      <c r="C52" s="7">
+        <f>H23</f>
+        <v/>
+      </c>
+      <c r="D52" s="7">
+        <f>D23</f>
+        <v/>
+      </c>
+      <c r="E52" s="7">
+        <f>E23</f>
+        <v/>
+      </c>
+      <c r="F52" s="7">
+        <f>G23</f>
+        <v/>
+      </c>
+      <c r="G52" s="7">
+        <f>IF(AND(C23&gt;=4,H23&gt;=4,D23="Yes",E23="Yes",G23="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Binary Search Tree</t>
+        </is>
+      </c>
+      <c r="B53" s="5">
+        <f>C24</f>
+        <v/>
+      </c>
+      <c r="C53" s="5">
+        <f>H24</f>
+        <v/>
+      </c>
+      <c r="D53" s="5">
+        <f>D24</f>
+        <v/>
+      </c>
+      <c r="E53" s="5">
+        <f>E24</f>
+        <v/>
+      </c>
+      <c r="F53" s="5">
+        <f>G24</f>
+        <v/>
+      </c>
+      <c r="G53" s="5">
+        <f>IF(AND(C24&gt;=4,H24&gt;=4,D24="Yes",E24="Yes",G24="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>Graph DFS</t>
+        </is>
+      </c>
+      <c r="B54" s="7">
+        <f>C25</f>
+        <v/>
+      </c>
+      <c r="C54" s="7">
+        <f>H25</f>
+        <v/>
+      </c>
+      <c r="D54" s="7">
+        <f>D25</f>
+        <v/>
+      </c>
+      <c r="E54" s="7">
+        <f>E25</f>
+        <v/>
+      </c>
+      <c r="F54" s="7">
+        <f>G25</f>
+        <v/>
+      </c>
+      <c r="G54" s="7">
+        <f>IF(AND(C25&gt;=4,H25&gt;=4,D25="Yes",E25="Yes",G25="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Graph BFS</t>
+        </is>
+      </c>
+      <c r="B55" s="5">
+        <f>C26</f>
+        <v/>
+      </c>
+      <c r="C55" s="5">
+        <f>H26</f>
+        <v/>
+      </c>
+      <c r="D55" s="5">
+        <f>D26</f>
+        <v/>
+      </c>
+      <c r="E55" s="5">
+        <f>E26</f>
+        <v/>
+      </c>
+      <c r="F55" s="5">
+        <f>G26</f>
+        <v/>
+      </c>
+      <c r="G55" s="5">
+        <f>IF(AND(C26&gt;=4,H26&gt;=4,D26="Yes",E26="Yes",G26="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Topological Sort</t>
+        </is>
+      </c>
+      <c r="B56" s="7">
+        <f>C27</f>
+        <v/>
+      </c>
+      <c r="C56" s="7">
+        <f>H27</f>
+        <v/>
+      </c>
+      <c r="D56" s="7">
+        <f>D27</f>
+        <v/>
+      </c>
+      <c r="E56" s="7">
+        <f>E27</f>
+        <v/>
+      </c>
+      <c r="F56" s="7">
+        <f>G27</f>
+        <v/>
+      </c>
+      <c r="G56" s="7">
+        <f>IF(AND(C27&gt;=4,H27&gt;=4,D27="Yes",E27="Yes",G27="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Union Find (Disjoint Set)</t>
+        </is>
+      </c>
+      <c r="B57" s="5">
+        <f>C28</f>
+        <v/>
+      </c>
+      <c r="C57" s="5">
+        <f>H28</f>
+        <v/>
+      </c>
+      <c r="D57" s="5">
+        <f>D28</f>
+        <v/>
+      </c>
+      <c r="E57" s="5">
+        <f>E28</f>
+        <v/>
+      </c>
+      <c r="F57" s="5">
+        <f>G28</f>
+        <v/>
+      </c>
+      <c r="G57" s="5">
+        <f>IF(AND(C28&gt;=4,H28&gt;=4,D28="Yes",E28="Yes",G28="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>Trie</t>
+        </is>
+      </c>
+      <c r="B58" s="7">
+        <f>C29</f>
+        <v/>
+      </c>
+      <c r="C58" s="7">
+        <f>H29</f>
+        <v/>
+      </c>
+      <c r="D58" s="7">
+        <f>D29</f>
+        <v/>
+      </c>
+      <c r="E58" s="7">
+        <f>E29</f>
+        <v/>
+      </c>
+      <c r="F58" s="7">
+        <f>G29</f>
+        <v/>
+      </c>
+      <c r="G58" s="7">
+        <f>IF(AND(C29&gt;=4,H29&gt;=4,D29="Yes",E29="Yes",G29="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Backtracking</t>
+        </is>
+      </c>
+      <c r="B59" s="5">
+        <f>C30</f>
+        <v/>
+      </c>
+      <c r="C59" s="5">
+        <f>H30</f>
+        <v/>
+      </c>
+      <c r="D59" s="5">
+        <f>D30</f>
+        <v/>
+      </c>
+      <c r="E59" s="5">
+        <f>E30</f>
+        <v/>
+      </c>
+      <c r="F59" s="5">
+        <f>G30</f>
+        <v/>
+      </c>
+      <c r="G59" s="5">
+        <f>IF(AND(C30&gt;=4,H30&gt;=4,D30="Yes",E30="Yes",G30="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>Greedy</t>
+        </is>
+      </c>
+      <c r="B60" s="7">
+        <f>C31</f>
+        <v/>
+      </c>
+      <c r="C60" s="7">
+        <f>H31</f>
+        <v/>
+      </c>
+      <c r="D60" s="7">
+        <f>D31</f>
+        <v/>
+      </c>
+      <c r="E60" s="7">
+        <f>E31</f>
+        <v/>
+      </c>
+      <c r="F60" s="7">
+        <f>G31</f>
+        <v/>
+      </c>
+      <c r="G60" s="7">
+        <f>IF(AND(C31&gt;=4,H31&gt;=4,D31="Yes",E31="Yes",G31="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Dynamic Programming</t>
+        </is>
+      </c>
+      <c r="B61" s="5">
+        <f>C32</f>
+        <v/>
+      </c>
+      <c r="C61" s="5">
+        <f>H32</f>
+        <v/>
+      </c>
+      <c r="D61" s="5">
+        <f>D32</f>
+        <v/>
+      </c>
+      <c r="E61" s="5">
+        <f>E32</f>
+        <v/>
+      </c>
+      <c r="F61" s="5">
+        <f>G32</f>
+        <v/>
+      </c>
+      <c r="G61" s="5">
+        <f>IF(AND(C32&gt;=4,H32&gt;=4,D32="Yes",E32="Yes",G32="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>Interval Problems</t>
+        </is>
+      </c>
+      <c r="B62" s="7">
+        <f>C33</f>
+        <v/>
+      </c>
+      <c r="C62" s="7">
+        <f>H33</f>
+        <v/>
+      </c>
+      <c r="D62" s="7">
+        <f>D33</f>
+        <v/>
+      </c>
+      <c r="E62" s="7">
+        <f>E33</f>
+        <v/>
+      </c>
+      <c r="F62" s="7">
+        <f>G33</f>
+        <v/>
+      </c>
+      <c r="G62" s="7">
+        <f>IF(AND(C33&gt;=4,H33&gt;=4,D33="Yes",E33="Yes",G33="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Matrix Problems</t>
+        </is>
+      </c>
+      <c r="B63" s="5">
+        <f>C34</f>
+        <v/>
+      </c>
+      <c r="C63" s="5">
+        <f>H34</f>
+        <v/>
+      </c>
+      <c r="D63" s="5">
+        <f>D34</f>
+        <v/>
+      </c>
+      <c r="E63" s="5">
+        <f>E34</f>
+        <v/>
+      </c>
+      <c r="F63" s="5">
+        <f>G34</f>
+        <v/>
+      </c>
+      <c r="G63" s="5">
+        <f>IF(AND(C34&gt;=4,H34&gt;=4,D34="Yes",E34="Yes",G34="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>Design Problems</t>
+        </is>
+      </c>
+      <c r="B64" s="7">
+        <f>C35</f>
+        <v/>
+      </c>
+      <c r="C64" s="7">
+        <f>H35</f>
+        <v/>
+      </c>
+      <c r="D64" s="7">
+        <f>D35</f>
+        <v/>
+      </c>
+      <c r="E64" s="7">
+        <f>E35</f>
+        <v/>
+      </c>
+      <c r="F64" s="7">
+        <f>G35</f>
+        <v/>
+      </c>
+      <c r="G64" s="7">
+        <f>IF(AND(C35&gt;=4,H35&gt;=4,D35="Yes",E35="Yes",G35="Yes"),"Interview Ready","Needs Revision")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="23" t="inlineStr">
+        <is>
+          <t>PATTERN READINESS LEVELS</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Pattern</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Advanced</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Interview Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Arrays &amp; Hashing</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n"/>
+      <c r="C68" s="5" t="n"/>
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="5" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Prefix Sum</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="n"/>
+      <c r="C69" s="7" t="n"/>
+      <c r="D69" s="7" t="n"/>
+      <c r="E69" s="7" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n"/>
+      <c r="C70" s="5" t="n"/>
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>Sliding Window</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="7" t="n"/>
+      <c r="E71" s="7" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Binary Search</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>Bit Manipulation</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="n"/>
+      <c r="C73" s="7" t="n"/>
+      <c r="D73" s="7" t="n"/>
+      <c r="E73" s="7" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Stack</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n"/>
+      <c r="C74" s="5" t="n"/>
+      <c r="D74" s="5" t="n"/>
+      <c r="E74" s="5" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>Monotonic Stack</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="n"/>
+      <c r="C75" s="7" t="n"/>
+      <c r="D75" s="7" t="n"/>
+      <c r="E75" s="7" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Queue</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n"/>
+      <c r="C76" s="5" t="n"/>
+      <c r="D76" s="5" t="n"/>
+      <c r="E76" s="5" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>Heap / Priority Queue</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="n"/>
+      <c r="C77" s="7" t="n"/>
+      <c r="D77" s="7" t="n"/>
+      <c r="E77" s="7" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Linked List</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n"/>
+      <c r="C78" s="5" t="n"/>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>Fast &amp; Slow Pointer</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="n"/>
+      <c r="C79" s="7" t="n"/>
+      <c r="D79" s="7" t="n"/>
+      <c r="E79" s="7" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Trees (DFS)</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n"/>
+      <c r="C80" s="5" t="n"/>
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="5" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>Trees (BFS)</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="n"/>
+      <c r="C81" s="7" t="n"/>
+      <c r="D81" s="7" t="n"/>
+      <c r="E81" s="7" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Binary Search Tree</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n"/>
+      <c r="C82" s="5" t="n"/>
+      <c r="D82" s="5" t="n"/>
+      <c r="E82" s="5" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>Graph DFS</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="n"/>
+      <c r="C83" s="7" t="n"/>
+      <c r="D83" s="7" t="n"/>
+      <c r="E83" s="7" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>Graph BFS</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n"/>
+      <c r="C84" s="5" t="n"/>
+      <c r="D84" s="5" t="n"/>
+      <c r="E84" s="5" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>Topological Sort</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="n"/>
+      <c r="C85" s="7" t="n"/>
+      <c r="D85" s="7" t="n"/>
+      <c r="E85" s="7" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Union Find (Disjoint Set)</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n"/>
+      <c r="C86" s="5" t="n"/>
+      <c r="D86" s="5" t="n"/>
+      <c r="E86" s="5" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>Trie</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="n"/>
+      <c r="C87" s="7" t="n"/>
+      <c r="D87" s="7" t="n"/>
+      <c r="E87" s="7" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Backtracking</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n"/>
+      <c r="C88" s="5" t="n"/>
+      <c r="D88" s="5" t="n"/>
+      <c r="E88" s="5" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>Greedy</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="n"/>
+      <c r="C89" s="7" t="n"/>
+      <c r="D89" s="7" t="n"/>
+      <c r="E89" s="7" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>Dynamic Programming</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n"/>
+      <c r="C90" s="5" t="n"/>
+      <c r="D90" s="5" t="n"/>
+      <c r="E90" s="5" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>Interval Problems</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="n"/>
+      <c r="C91" s="7" t="n"/>
+      <c r="D91" s="7" t="n"/>
+      <c r="E91" s="7" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>Matrix Problems</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n"/>
+      <c r="C92" s="5" t="n"/>
+      <c r="D92" s="5" t="n"/>
+      <c r="E92" s="5" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>Design Problems</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="n"/>
+      <c r="C93" s="7" t="n"/>
+      <c r="D93" s="7" t="n"/>
+      <c r="E93" s="7" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="23" t="inlineStr">
+        <is>
+          <t>PATTERN MASTERY CHECKLISTS — Sub-skill breakdown per pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="30" t="inlineStr">
+        <is>
+          <t>Arrays &amp; Hashing</t>
+        </is>
+      </c>
+      <c r="B96" s="31" t="n"/>
+      <c r="C96" s="31" t="n"/>
+      <c r="D96" s="31" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>HashMap for O(1) lookup</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="n"/>
+      <c r="D98" s="5" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>Frequency counting</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="n"/>
+      <c r="D99" s="7" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Prefix/suffix product</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="n"/>
+      <c r="D100" s="5" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>Sorting + scan</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="n"/>
+      <c r="D101" s="7" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>Bucket sort</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="n"/>
+      <c r="D102" s="5" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>Two-pass techniques</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="n"/>
+      <c r="D103" s="7" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>In-place modification</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="n"/>
+      <c r="D104" s="5" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>Duplicate detection</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="n"/>
+      <c r="D105" s="7" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="30" t="inlineStr">
+        <is>
+          <t>Prefix Sum</t>
+        </is>
+      </c>
+      <c r="B107" s="31" t="n"/>
+      <c r="C107" s="31" t="n"/>
+      <c r="D107" s="31" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>Basic prefix sum</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="n"/>
+      <c r="D109" s="5" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>Range sum queries</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="n"/>
+      <c r="D110" s="7" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>Subarray sum equals K</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="n"/>
+      <c r="D111" s="5" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>2D prefix sum</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="n"/>
+      <c r="D112" s="7" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>Prefix XOR</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="n"/>
+      <c r="D113" s="5" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>Difference array</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="n"/>
+      <c r="D114" s="7" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>Running average</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="n"/>
+      <c r="D115" s="5" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="30" t="inlineStr">
+        <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="B117" s="31" t="n"/>
+      <c r="C117" s="31" t="n"/>
+      <c r="D117" s="31" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>Opposite-end pointers</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="n"/>
+      <c r="D119" s="5" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>Same-direction pointers</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="n"/>
+      <c r="D120" s="7" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>Dutch National Flag</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="n"/>
+      <c r="D121" s="5" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>Three pointers (3Sum)</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="n"/>
+      <c r="D122" s="7" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>Expand from center</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="n"/>
+      <c r="D123" s="5" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>Merge two sorted</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="n"/>
+      <c r="D124" s="7" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>Partition in-place</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="n"/>
+      <c r="D125" s="5" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="30" t="inlineStr">
+        <is>
+          <t>Sliding Window</t>
+        </is>
+      </c>
+      <c r="B127" s="31" t="n"/>
+      <c r="C127" s="31" t="n"/>
+      <c r="D127" s="31" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>Fixed-size window</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="n"/>
+      <c r="D129" s="5" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>Variable-size window</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="n"/>
+      <c r="D130" s="7" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>Character frequency window</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="n"/>
+      <c r="D131" s="5" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>Distinct elements window</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="n"/>
+      <c r="D132" s="7" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>Window shrinking condition</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="n"/>
+      <c r="D133" s="5" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>Monotonic queue in window</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="n"/>
+      <c r="D134" s="7" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>Prefix sum + window</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="n"/>
+      <c r="D135" s="5" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t>Binary search + window</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="n"/>
+      <c r="D136" s="7" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="30" t="inlineStr">
+        <is>
+          <t>Binary Search</t>
+        </is>
+      </c>
+      <c r="B138" s="31" t="n"/>
+      <c r="C138" s="31" t="n"/>
+      <c r="D138" s="31" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>Classic binary search</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="n"/>
+      <c r="D140" s="5" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B141" s="8" t="inlineStr">
+        <is>
+          <t>Lower bound (leftmost)</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="n"/>
+      <c r="D141" s="7" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>Upper bound (rightmost)</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="n"/>
+      <c r="D142" s="5" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B143" s="8" t="inlineStr">
+        <is>
+          <t>Rotated sorted arrays</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="n"/>
+      <c r="D143" s="7" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>Binary search on answer</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="n"/>
+      <c r="D144" s="5" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B145" s="8" t="inlineStr">
+        <is>
+          <t>Peak/valley problems</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="n"/>
+      <c r="D145" s="7" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>Infinite search space</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="n"/>
+      <c r="D146" s="5" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B147" s="8" t="inlineStr">
+        <is>
+          <t>Matrix binary search</t>
+        </is>
+      </c>
+      <c r="C147" s="7" t="n"/>
+      <c r="D147" s="7" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="30" t="inlineStr">
+        <is>
+          <t>Bit Manipulation</t>
+        </is>
+      </c>
+      <c r="B149" s="31" t="n"/>
+      <c r="C149" s="31" t="n"/>
+      <c r="D149" s="31" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>XOR for uniqueness</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="n"/>
+      <c r="D151" s="5" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B152" s="8" t="inlineStr">
+        <is>
+          <t>Brian Kernighan's trick</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="n"/>
+      <c r="D152" s="7" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>Bit counting</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="n"/>
+      <c r="D153" s="5" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B154" s="8" t="inlineStr">
+        <is>
+          <t>Carry-free addition</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="n"/>
+      <c r="D154" s="7" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B155" s="6" t="inlineStr">
+        <is>
+          <t>Power of 2 checks</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="n"/>
+      <c r="D155" s="5" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B156" s="8" t="inlineStr">
+        <is>
+          <t>Bit masking</t>
+        </is>
+      </c>
+      <c r="C156" s="7" t="n"/>
+      <c r="D156" s="7" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t>Subset generation via bits</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="n"/>
+      <c r="D157" s="5" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="30" t="inlineStr">
+        <is>
+          <t>Stack</t>
+        </is>
+      </c>
+      <c r="B159" s="31" t="n"/>
+      <c r="C159" s="31" t="n"/>
+      <c r="D159" s="31" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>Balanced parentheses</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="n"/>
+      <c r="D161" s="5" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B162" s="8" t="inlineStr">
+        <is>
+          <t>Expression evaluation</t>
+        </is>
+      </c>
+      <c r="C162" s="7" t="n"/>
+      <c r="D162" s="7" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t>Nested structure parsing</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="n"/>
+      <c r="D163" s="5" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B164" s="8" t="inlineStr">
+        <is>
+          <t>Undo/redo simulation</t>
+        </is>
+      </c>
+      <c r="C164" s="7" t="n"/>
+      <c r="D164" s="7" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B165" s="6" t="inlineStr">
+        <is>
+          <t>Min/max stack</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="n"/>
+      <c r="D165" s="5" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B166" s="8" t="inlineStr">
+        <is>
+          <t>Function call simulation</t>
+        </is>
+      </c>
+      <c r="C166" s="7" t="n"/>
+      <c r="D166" s="7" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="30" t="inlineStr">
+        <is>
+          <t>Monotonic Stack</t>
+        </is>
+      </c>
+      <c r="B168" s="31" t="n"/>
+      <c r="C168" s="31" t="n"/>
+      <c r="D168" s="31" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t>Next greater element</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="n"/>
+      <c r="D170" s="5" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B171" s="8" t="inlineStr">
+        <is>
+          <t>Next smaller element</t>
+        </is>
+      </c>
+      <c r="C171" s="7" t="n"/>
+      <c r="D171" s="7" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
+          <t>Largest rectangle</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="n"/>
+      <c r="D172" s="5" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B173" s="8" t="inlineStr">
+        <is>
+          <t>Stock span</t>
+        </is>
+      </c>
+      <c r="C173" s="7" t="n"/>
+      <c r="D173" s="7" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B174" s="6" t="inlineStr">
+        <is>
+          <t>Temperature problems</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="n"/>
+      <c r="D174" s="5" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B175" s="8" t="inlineStr">
+        <is>
+          <t>Sum of subarray min/max</t>
+        </is>
+      </c>
+      <c r="C175" s="7" t="n"/>
+      <c r="D175" s="7" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>Contribution technique</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="n"/>
+      <c r="D176" s="5" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="30" t="inlineStr">
+        <is>
+          <t>Queue</t>
+        </is>
+      </c>
+      <c r="B178" s="31" t="n"/>
+      <c r="C178" s="31" t="n"/>
+      <c r="D178" s="31" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
+        <is>
+          <t>BFS level-order</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="n"/>
+      <c r="D180" s="5" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B181" s="8" t="inlineStr">
+        <is>
+          <t>Circular queue</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="n"/>
+      <c r="D181" s="7" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B182" s="6" t="inlineStr">
+        <is>
+          <t>Priority scheduling</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="n"/>
+      <c r="D182" s="5" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B183" s="8" t="inlineStr">
+        <is>
+          <t>Sliding window via deque</t>
+        </is>
+      </c>
+      <c r="C183" s="7" t="n"/>
+      <c r="D183" s="7" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B184" s="6" t="inlineStr">
+        <is>
+          <t>Task processing order</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="n"/>
+      <c r="D184" s="5" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="30" t="inlineStr">
+        <is>
+          <t>Heap / Priority Queue</t>
+        </is>
+      </c>
+      <c r="B186" s="31" t="n"/>
+      <c r="C186" s="31" t="n"/>
+      <c r="D186" s="31" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
+        <is>
+          <t>Kth largest/smallest</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="n"/>
+      <c r="D188" s="5" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B189" s="8" t="inlineStr">
+        <is>
+          <t>Top K elements</t>
+        </is>
+      </c>
+      <c r="C189" s="7" t="n"/>
+      <c r="D189" s="7" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
+        <is>
+          <t>Two-heap median</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="n"/>
+      <c r="D190" s="5" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B191" s="8" t="inlineStr">
+        <is>
+          <t>Merge K sorted</t>
+        </is>
+      </c>
+      <c r="C191" s="7" t="n"/>
+      <c r="D191" s="7" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B192" s="6" t="inlineStr">
+        <is>
+          <t>Event-driven simulation</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="n"/>
+      <c r="D192" s="5" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B193" s="8" t="inlineStr">
+        <is>
+          <t>Greedy + heap combo</t>
+        </is>
+      </c>
+      <c r="C193" s="7" t="n"/>
+      <c r="D193" s="7" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B194" s="6" t="inlineStr">
+        <is>
+          <t>Lazy deletion</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="n"/>
+      <c r="D194" s="5" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="30" t="inlineStr">
+        <is>
+          <t>Linked List</t>
+        </is>
+      </c>
+      <c r="B196" s="31" t="n"/>
+      <c r="C196" s="31" t="n"/>
+      <c r="D196" s="31" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B198" s="6" t="inlineStr">
+        <is>
+          <t>Iterative reversal</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="n"/>
+      <c r="D198" s="5" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B199" s="8" t="inlineStr">
+        <is>
+          <t>Recursive reversal</t>
+        </is>
+      </c>
+      <c r="C199" s="7" t="n"/>
+      <c r="D199" s="7" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B200" s="6" t="inlineStr">
+        <is>
+          <t>Dummy head technique</t>
+        </is>
+      </c>
+      <c r="C200" s="5" t="n"/>
+      <c r="D200" s="5" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B201" s="8" t="inlineStr">
+        <is>
+          <t>Two-pointer (gap)</t>
+        </is>
+      </c>
+      <c r="C201" s="7" t="n"/>
+      <c r="D201" s="7" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B202" s="6" t="inlineStr">
+        <is>
+          <t>Deep copy with random</t>
+        </is>
+      </c>
+      <c r="C202" s="5" t="n"/>
+      <c r="D202" s="5" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B203" s="8" t="inlineStr">
+        <is>
+          <t>Merge sorted lists</t>
+        </is>
+      </c>
+      <c r="C203" s="7" t="n"/>
+      <c r="D203" s="7" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B204" s="6" t="inlineStr">
+        <is>
+          <t>K-group reversal</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="n"/>
+      <c r="D204" s="5" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="30" t="inlineStr">
+        <is>
+          <t>Fast &amp; Slow Pointer</t>
+        </is>
+      </c>
+      <c r="B206" s="31" t="n"/>
+      <c r="C206" s="31" t="n"/>
+      <c r="D206" s="31" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D207" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B208" s="6" t="inlineStr">
+        <is>
+          <t>Cycle detection (Floyd's)</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="n"/>
+      <c r="D208" s="5" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B209" s="8" t="inlineStr">
+        <is>
+          <t>Cycle start finding</t>
+        </is>
+      </c>
+      <c r="C209" s="7" t="n"/>
+      <c r="D209" s="7" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B210" s="6" t="inlineStr">
+        <is>
+          <t>Middle of list</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="n"/>
+      <c r="D210" s="5" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B211" s="8" t="inlineStr">
+        <is>
+          <t>Happy number</t>
+        </is>
+      </c>
+      <c r="C211" s="7" t="n"/>
+      <c r="D211" s="7" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
+        <is>
+          <t>Duplicate in array</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="n"/>
+      <c r="D212" s="5" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="30" t="inlineStr">
+        <is>
+          <t>Trees (DFS)</t>
+        </is>
+      </c>
+      <c r="B214" s="31" t="n"/>
+      <c r="C214" s="31" t="n"/>
+      <c r="D214" s="31" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D215" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B216" s="6" t="inlineStr">
+        <is>
+          <t>Preorder traversal</t>
+        </is>
+      </c>
+      <c r="C216" s="5" t="n"/>
+      <c r="D216" s="5" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B217" s="8" t="inlineStr">
+        <is>
+          <t>Inorder traversal</t>
+        </is>
+      </c>
+      <c r="C217" s="7" t="n"/>
+      <c r="D217" s="7" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B218" s="6" t="inlineStr">
+        <is>
+          <t>Postorder traversal</t>
+        </is>
+      </c>
+      <c r="C218" s="5" t="n"/>
+      <c r="D218" s="5" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B219" s="8" t="inlineStr">
+        <is>
+          <t>Path sum problems</t>
+        </is>
+      </c>
+      <c r="C219" s="7" t="n"/>
+      <c r="D219" s="7" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B220" s="6" t="inlineStr">
+        <is>
+          <t>Tree diameter</t>
+        </is>
+      </c>
+      <c r="C220" s="5" t="n"/>
+      <c r="D220" s="5" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B221" s="8" t="inlineStr">
+        <is>
+          <t>Maximum path sum</t>
+        </is>
+      </c>
+      <c r="C221" s="7" t="n"/>
+      <c r="D221" s="7" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B222" s="6" t="inlineStr">
+        <is>
+          <t>Subtree problems</t>
+        </is>
+      </c>
+      <c r="C222" s="5" t="n"/>
+      <c r="D222" s="5" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B223" s="8" t="inlineStr">
+        <is>
+          <t>Tree serialization</t>
+        </is>
+      </c>
+      <c r="C223" s="7" t="n"/>
+      <c r="D223" s="7" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="30" t="inlineStr">
+        <is>
+          <t>Trees (BFS)</t>
+        </is>
+      </c>
+      <c r="B225" s="31" t="n"/>
+      <c r="C225" s="31" t="n"/>
+      <c r="D225" s="31" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D226" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B227" s="6" t="inlineStr">
+        <is>
+          <t>Level-order traversal</t>
+        </is>
+      </c>
+      <c r="C227" s="5" t="n"/>
+      <c r="D227" s="5" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B228" s="8" t="inlineStr">
+        <is>
+          <t>Right/left side view</t>
+        </is>
+      </c>
+      <c r="C228" s="7" t="n"/>
+      <c r="D228" s="7" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B229" s="6" t="inlineStr">
+        <is>
+          <t>Zigzag traversal</t>
+        </is>
+      </c>
+      <c r="C229" s="5" t="n"/>
+      <c r="D229" s="5" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B230" s="8" t="inlineStr">
+        <is>
+          <t>Minimum depth</t>
+        </is>
+      </c>
+      <c r="C230" s="7" t="n"/>
+      <c r="D230" s="7" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B231" s="6" t="inlineStr">
+        <is>
+          <t>Connect next pointers</t>
+        </is>
+      </c>
+      <c r="C231" s="5" t="n"/>
+      <c r="D231" s="5" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B232" s="8" t="inlineStr">
+        <is>
+          <t>Level averages</t>
+        </is>
+      </c>
+      <c r="C232" s="7" t="n"/>
+      <c r="D232" s="7" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="30" t="inlineStr">
+        <is>
+          <t>Binary Search Tree</t>
+        </is>
+      </c>
+      <c r="B234" s="31" t="n"/>
+      <c r="C234" s="31" t="n"/>
+      <c r="D234" s="31" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B235" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D235" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B236" s="6" t="inlineStr">
+        <is>
+          <t>BST validation</t>
+        </is>
+      </c>
+      <c r="C236" s="5" t="n"/>
+      <c r="D236" s="5" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B237" s="8" t="inlineStr">
+        <is>
+          <t>Inorder = sorted property</t>
+        </is>
+      </c>
+      <c r="C237" s="7" t="n"/>
+      <c r="D237" s="7" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B238" s="6" t="inlineStr">
+        <is>
+          <t>Kth smallest/largest</t>
+        </is>
+      </c>
+      <c r="C238" s="5" t="n"/>
+      <c r="D238" s="5" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B239" s="8" t="inlineStr">
+        <is>
+          <t>LCA in BST</t>
+        </is>
+      </c>
+      <c r="C239" s="7" t="n"/>
+      <c r="D239" s="7" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B240" s="6" t="inlineStr">
+        <is>
+          <t>BST insert/delete</t>
+        </is>
+      </c>
+      <c r="C240" s="5" t="n"/>
+      <c r="D240" s="5" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B241" s="8" t="inlineStr">
+        <is>
+          <t>Balanced BST construction</t>
+        </is>
+      </c>
+      <c r="C241" s="7" t="n"/>
+      <c r="D241" s="7" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="30" t="inlineStr">
+        <is>
+          <t>Graph DFS</t>
+        </is>
+      </c>
+      <c r="B243" s="31" t="n"/>
+      <c r="C243" s="31" t="n"/>
+      <c r="D243" s="31" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D244" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B245" s="6" t="inlineStr">
+        <is>
+          <t>Connected components</t>
+        </is>
+      </c>
+      <c r="C245" s="5" t="n"/>
+      <c r="D245" s="5" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B246" s="8" t="inlineStr">
+        <is>
+          <t>Island counting</t>
+        </is>
+      </c>
+      <c r="C246" s="7" t="n"/>
+      <c r="D246" s="7" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B247" s="6" t="inlineStr">
+        <is>
+          <t>Flood fill</t>
+        </is>
+      </c>
+      <c r="C247" s="5" t="n"/>
+      <c r="D247" s="5" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B248" s="8" t="inlineStr">
+        <is>
+          <t>Cycle detection (directed)</t>
+        </is>
+      </c>
+      <c r="C248" s="7" t="n"/>
+      <c r="D248" s="7" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B249" s="6" t="inlineStr">
+        <is>
+          <t>Cycle detection (undirected)</t>
+        </is>
+      </c>
+      <c r="C249" s="5" t="n"/>
+      <c r="D249" s="5" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B250" s="8" t="inlineStr">
+        <is>
+          <t>Path existence</t>
+        </is>
+      </c>
+      <c r="C250" s="7" t="n"/>
+      <c r="D250" s="7" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B251" s="6" t="inlineStr">
+        <is>
+          <t>All paths source to target</t>
+        </is>
+      </c>
+      <c r="C251" s="5" t="n"/>
+      <c r="D251" s="5" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B252" s="8" t="inlineStr">
+        <is>
+          <t>Articulation points</t>
+        </is>
+      </c>
+      <c r="C252" s="7" t="n"/>
+      <c r="D252" s="7" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="30" t="inlineStr">
+        <is>
+          <t>Graph BFS</t>
+        </is>
+      </c>
+      <c r="B254" s="31" t="n"/>
+      <c r="C254" s="31" t="n"/>
+      <c r="D254" s="31" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D255" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B256" s="6" t="inlineStr">
+        <is>
+          <t>Shortest path unweighted</t>
+        </is>
+      </c>
+      <c r="C256" s="5" t="n"/>
+      <c r="D256" s="5" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B257" s="8" t="inlineStr">
+        <is>
+          <t>Multi-source BFS</t>
+        </is>
+      </c>
+      <c r="C257" s="7" t="n"/>
+      <c r="D257" s="7" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B258" s="6" t="inlineStr">
+        <is>
+          <t>Rotting oranges pattern</t>
+        </is>
+      </c>
+      <c r="C258" s="5" t="n"/>
+      <c r="D258" s="5" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B259" s="8" t="inlineStr">
+        <is>
+          <t>Word ladder pattern</t>
+        </is>
+      </c>
+      <c r="C259" s="7" t="n"/>
+      <c r="D259" s="7" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B260" s="6" t="inlineStr">
+        <is>
+          <t>Level-by-level processing</t>
+        </is>
+      </c>
+      <c r="C260" s="5" t="n"/>
+      <c r="D260" s="5" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B261" s="8" t="inlineStr">
+        <is>
+          <t>0-1 BFS</t>
+        </is>
+      </c>
+      <c r="C261" s="7" t="n"/>
+      <c r="D261" s="7" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="30" t="inlineStr">
+        <is>
+          <t>Topological Sort</t>
+        </is>
+      </c>
+      <c r="B263" s="31" t="n"/>
+      <c r="C263" s="31" t="n"/>
+      <c r="D263" s="31" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B264" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D264" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B265" s="6" t="inlineStr">
+        <is>
+          <t>Kahn's algorithm (BFS)</t>
+        </is>
+      </c>
+      <c r="C265" s="5" t="n"/>
+      <c r="D265" s="5" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B266" s="8" t="inlineStr">
+        <is>
+          <t>DFS-based topo sort</t>
+        </is>
+      </c>
+      <c r="C266" s="7" t="n"/>
+      <c r="D266" s="7" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B267" s="6" t="inlineStr">
+        <is>
+          <t>Cycle detection in DAG</t>
+        </is>
+      </c>
+      <c r="C267" s="5" t="n"/>
+      <c r="D267" s="5" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B268" s="8" t="inlineStr">
+        <is>
+          <t>Course scheduling</t>
+        </is>
+      </c>
+      <c r="C268" s="7" t="n"/>
+      <c r="D268" s="7" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B269" s="6" t="inlineStr">
+        <is>
+          <t>Build order</t>
+        </is>
+      </c>
+      <c r="C269" s="5" t="n"/>
+      <c r="D269" s="5" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B270" s="8" t="inlineStr">
+        <is>
+          <t>Alien dictionary</t>
+        </is>
+      </c>
+      <c r="C270" s="7" t="n"/>
+      <c r="D270" s="7" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="30" t="inlineStr">
+        <is>
+          <t>Union Find (Disjoint Set)</t>
+        </is>
+      </c>
+      <c r="B272" s="31" t="n"/>
+      <c r="C272" s="31" t="n"/>
+      <c r="D272" s="31" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D273" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B274" s="6" t="inlineStr">
+        <is>
+          <t>Path compression</t>
+        </is>
+      </c>
+      <c r="C274" s="5" t="n"/>
+      <c r="D274" s="5" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B275" s="8" t="inlineStr">
+        <is>
+          <t>Union by rank</t>
+        </is>
+      </c>
+      <c r="C275" s="7" t="n"/>
+      <c r="D275" s="7" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B276" s="6" t="inlineStr">
+        <is>
+          <t>Connected components count</t>
+        </is>
+      </c>
+      <c r="C276" s="5" t="n"/>
+      <c r="D276" s="5" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B277" s="8" t="inlineStr">
+        <is>
+          <t>Redundant edge detection</t>
+        </is>
+      </c>
+      <c r="C277" s="7" t="n"/>
+      <c r="D277" s="7" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B278" s="6" t="inlineStr">
+        <is>
+          <t>Accounts merge pattern</t>
+        </is>
+      </c>
+      <c r="C278" s="5" t="n"/>
+      <c r="D278" s="5" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B279" s="8" t="inlineStr">
+        <is>
+          <t>Dynamic connectivity</t>
+        </is>
+      </c>
+      <c r="C279" s="7" t="n"/>
+      <c r="D279" s="7" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B280" s="6" t="inlineStr">
+        <is>
+          <t>MST (Kruskal's)</t>
+        </is>
+      </c>
+      <c r="C280" s="5" t="n"/>
+      <c r="D280" s="5" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="30" t="inlineStr">
+        <is>
+          <t>Trie</t>
+        </is>
+      </c>
+      <c r="B282" s="31" t="n"/>
+      <c r="C282" s="31" t="n"/>
+      <c r="D282" s="31" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B283" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C283" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D283" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B284" s="6" t="inlineStr">
+        <is>
+          <t>Insert/search/prefix</t>
+        </is>
+      </c>
+      <c r="C284" s="5" t="n"/>
+      <c r="D284" s="5" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B285" s="8" t="inlineStr">
+        <is>
+          <t>Wildcard matching with DFS</t>
+        </is>
+      </c>
+      <c r="C285" s="7" t="n"/>
+      <c r="D285" s="7" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B286" s="6" t="inlineStr">
+        <is>
+          <t>Word search in grid</t>
+        </is>
+      </c>
+      <c r="C286" s="5" t="n"/>
+      <c r="D286" s="5" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B287" s="8" t="inlineStr">
+        <is>
+          <t>Autocomplete system</t>
+        </is>
+      </c>
+      <c r="C287" s="7" t="n"/>
+      <c r="D287" s="7" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B288" s="6" t="inlineStr">
+        <is>
+          <t>Longest common prefix</t>
+        </is>
+      </c>
+      <c r="C288" s="5" t="n"/>
+      <c r="D288" s="5" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B289" s="8" t="inlineStr">
+        <is>
+          <t>Count words with prefix</t>
+        </is>
+      </c>
+      <c r="C289" s="7" t="n"/>
+      <c r="D289" s="7" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="30" t="inlineStr">
+        <is>
+          <t>Backtracking</t>
+        </is>
+      </c>
+      <c r="B291" s="31" t="n"/>
+      <c r="C291" s="31" t="n"/>
+      <c r="D291" s="31" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B292" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C292" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D292" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B293" s="6" t="inlineStr">
+        <is>
+          <t>Subsets generation</t>
+        </is>
+      </c>
+      <c r="C293" s="5" t="n"/>
+      <c r="D293" s="5" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B294" s="8" t="inlineStr">
+        <is>
+          <t>Permutations</t>
+        </is>
+      </c>
+      <c r="C294" s="7" t="n"/>
+      <c r="D294" s="7" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B295" s="6" t="inlineStr">
+        <is>
+          <t>Combinations</t>
+        </is>
+      </c>
+      <c r="C295" s="5" t="n"/>
+      <c r="D295" s="5" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B296" s="8" t="inlineStr">
+        <is>
+          <t>Constraint satisfaction</t>
+        </is>
+      </c>
+      <c r="C296" s="7" t="n"/>
+      <c r="D296" s="7" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B297" s="6" t="inlineStr">
+        <is>
+          <t>Pruning strategies</t>
+        </is>
+      </c>
+      <c r="C297" s="5" t="n"/>
+      <c r="D297" s="5" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B298" s="8" t="inlineStr">
+        <is>
+          <t>State restoration</t>
+        </is>
+      </c>
+      <c r="C298" s="7" t="n"/>
+      <c r="D298" s="7" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B299" s="6" t="inlineStr">
+        <is>
+          <t>Grid path exploration</t>
+        </is>
+      </c>
+      <c r="C299" s="5" t="n"/>
+      <c r="D299" s="5" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B300" s="8" t="inlineStr">
+        <is>
+          <t>N-Queens pattern</t>
+        </is>
+      </c>
+      <c r="C300" s="7" t="n"/>
+      <c r="D300" s="7" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="30" t="inlineStr">
+        <is>
+          <t>Greedy</t>
+        </is>
+      </c>
+      <c r="B302" s="31" t="n"/>
+      <c r="C302" s="31" t="n"/>
+      <c r="D302" s="31" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D303" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B304" s="6" t="inlineStr">
+        <is>
+          <t>Activity selection</t>
+        </is>
+      </c>
+      <c r="C304" s="5" t="n"/>
+      <c r="D304" s="5" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B305" s="8" t="inlineStr">
+        <is>
+          <t>Jump game pattern</t>
+        </is>
+      </c>
+      <c r="C305" s="7" t="n"/>
+      <c r="D305" s="7" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B306" s="6" t="inlineStr">
+        <is>
+          <t>Interval scheduling</t>
+        </is>
+      </c>
+      <c r="C306" s="5" t="n"/>
+      <c r="D306" s="5" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B307" s="8" t="inlineStr">
+        <is>
+          <t>Huffman-style greedy</t>
+        </is>
+      </c>
+      <c r="C307" s="7" t="n"/>
+      <c r="D307" s="7" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B308" s="6" t="inlineStr">
+        <is>
+          <t>Exchange argument proof</t>
+        </is>
+      </c>
+      <c r="C308" s="5" t="n"/>
+      <c r="D308" s="5" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B309" s="8" t="inlineStr">
+        <is>
+          <t>Kadane's algorithm</t>
+        </is>
+      </c>
+      <c r="C309" s="7" t="n"/>
+      <c r="D309" s="7" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B310" s="6" t="inlineStr">
+        <is>
+          <t>Task scheduling</t>
+        </is>
+      </c>
+      <c r="C310" s="5" t="n"/>
+      <c r="D310" s="5" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="30" t="inlineStr">
+        <is>
+          <t>Dynamic Programming</t>
+        </is>
+      </c>
+      <c r="B312" s="31" t="n"/>
+      <c r="C312" s="31" t="n"/>
+      <c r="D312" s="31" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B313" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C313" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D313" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B314" s="6" t="inlineStr">
+        <is>
+          <t>1D linear DP</t>
+        </is>
+      </c>
+      <c r="C314" s="5" t="n"/>
+      <c r="D314" s="5" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B315" s="8" t="inlineStr">
+        <is>
+          <t>2D grid DP</t>
+        </is>
+      </c>
+      <c r="C315" s="7" t="n"/>
+      <c r="D315" s="7" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B316" s="6" t="inlineStr">
+        <is>
+          <t>Knapsack (0/1 and unbounded)</t>
+        </is>
+      </c>
+      <c r="C316" s="5" t="n"/>
+      <c r="D316" s="5" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B317" s="8" t="inlineStr">
+        <is>
+          <t>String DP (LCS/edit distance)</t>
+        </is>
+      </c>
+      <c r="C317" s="7" t="n"/>
+      <c r="D317" s="7" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B318" s="6" t="inlineStr">
+        <is>
+          <t>Interval DP</t>
+        </is>
+      </c>
+      <c r="C318" s="5" t="n"/>
+      <c r="D318" s="5" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B319" s="8" t="inlineStr">
+        <is>
+          <t>State machine DP (stocks)</t>
+        </is>
+      </c>
+      <c r="C319" s="7" t="n"/>
+      <c r="D319" s="7" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B320" s="6" t="inlineStr">
+        <is>
+          <t>Bitmask DP</t>
+        </is>
+      </c>
+      <c r="C320" s="5" t="n"/>
+      <c r="D320" s="5" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B321" s="8" t="inlineStr">
+        <is>
+          <t>Digit DP</t>
+        </is>
+      </c>
+      <c r="C321" s="7" t="n"/>
+      <c r="D321" s="7" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B322" s="6" t="inlineStr">
+        <is>
+          <t>Tree DP</t>
+        </is>
+      </c>
+      <c r="C322" s="5" t="n"/>
+      <c r="D322" s="5" t="n"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="30" t="inlineStr">
+        <is>
+          <t>Interval Problems</t>
+        </is>
+      </c>
+      <c r="B324" s="31" t="n"/>
+      <c r="C324" s="31" t="n"/>
+      <c r="D324" s="31" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B325" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C325" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D325" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B326" s="6" t="inlineStr">
+        <is>
+          <t>Sort by start time</t>
+        </is>
+      </c>
+      <c r="C326" s="5" t="n"/>
+      <c r="D326" s="5" t="n"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B327" s="8" t="inlineStr">
+        <is>
+          <t>Sort by end time</t>
+        </is>
+      </c>
+      <c r="C327" s="7" t="n"/>
+      <c r="D327" s="7" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B328" s="6" t="inlineStr">
+        <is>
+          <t>Merge overlapping</t>
+        </is>
+      </c>
+      <c r="C328" s="5" t="n"/>
+      <c r="D328" s="5" t="n"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B329" s="8" t="inlineStr">
+        <is>
+          <t>Insert interval</t>
+        </is>
+      </c>
+      <c r="C329" s="7" t="n"/>
+      <c r="D329" s="7" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B330" s="6" t="inlineStr">
+        <is>
+          <t>Non-overlapping selection</t>
+        </is>
+      </c>
+      <c r="C330" s="5" t="n"/>
+      <c r="D330" s="5" t="n"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B331" s="8" t="inlineStr">
+        <is>
+          <t>Line sweep</t>
+        </is>
+      </c>
+      <c r="C331" s="7" t="n"/>
+      <c r="D331" s="7" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B332" s="6" t="inlineStr">
+        <is>
+          <t>Meeting rooms pattern</t>
+        </is>
+      </c>
+      <c r="C332" s="5" t="n"/>
+      <c r="D332" s="5" t="n"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="30" t="inlineStr">
+        <is>
+          <t>Matrix Problems</t>
+        </is>
+      </c>
+      <c r="B334" s="31" t="n"/>
+      <c r="C334" s="31" t="n"/>
+      <c r="D334" s="31" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B335" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C335" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D335" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B336" s="6" t="inlineStr">
+        <is>
+          <t>Rotation (90/180/270)</t>
+        </is>
+      </c>
+      <c r="C336" s="5" t="n"/>
+      <c r="D336" s="5" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B337" s="8" t="inlineStr">
+        <is>
+          <t>Spiral traversal</t>
+        </is>
+      </c>
+      <c r="C337" s="7" t="n"/>
+      <c r="D337" s="7" t="n"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B338" s="6" t="inlineStr">
+        <is>
+          <t>Set matrix zeroes</t>
+        </is>
+      </c>
+      <c r="C338" s="5" t="n"/>
+      <c r="D338" s="5" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B339" s="8" t="inlineStr">
+        <is>
+          <t>Search in 2D matrix</t>
+        </is>
+      </c>
+      <c r="C339" s="7" t="n"/>
+      <c r="D339" s="7" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B340" s="6" t="inlineStr">
+        <is>
+          <t>Diagonal traversal</t>
+        </is>
+      </c>
+      <c r="C340" s="5" t="n"/>
+      <c r="D340" s="5" t="n"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B341" s="8" t="inlineStr">
+        <is>
+          <t>Layer-by-layer processing</t>
+        </is>
+      </c>
+      <c r="C341" s="7" t="n"/>
+      <c r="D341" s="7" t="n"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="30" t="inlineStr">
+        <is>
+          <t>Design Problems</t>
+        </is>
+      </c>
+      <c r="B343" s="31" t="n"/>
+      <c r="C343" s="31" t="n"/>
+      <c r="D343" s="31" t="n"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B344" s="4" t="inlineStr">
+        <is>
+          <t>Sub-skill</t>
+        </is>
+      </c>
+      <c r="C344" s="4" t="inlineStr">
+        <is>
+          <t>Mastered?</t>
+        </is>
+      </c>
+      <c r="D344" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B345" s="6" t="inlineStr">
+        <is>
+          <t>LRU/LFU cache</t>
+        </is>
+      </c>
+      <c r="C345" s="5" t="n"/>
+      <c r="D345" s="5" t="n"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B346" s="8" t="inlineStr">
+        <is>
+          <t>HashMap from scratch</t>
+        </is>
+      </c>
+      <c r="C346" s="7" t="n"/>
+      <c r="D346" s="7" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B347" s="6" t="inlineStr">
+        <is>
+          <t>Trie-based design</t>
+        </is>
+      </c>
+      <c r="C347" s="5" t="n"/>
+      <c r="D347" s="5" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B348" s="8" t="inlineStr">
+        <is>
+          <t>Random O(1) insert/delete</t>
+        </is>
+      </c>
+      <c r="C348" s="7" t="n"/>
+      <c r="D348" s="7" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B349" s="6" t="inlineStr">
+        <is>
+          <t>Snapshot versioning</t>
+        </is>
+      </c>
+      <c r="C349" s="5" t="n"/>
+      <c r="D349" s="5" t="n"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B350" s="8" t="inlineStr">
+        <is>
+          <t>Time-based key-value</t>
+        </is>
+      </c>
+      <c r="C350" s="7" t="n"/>
+      <c r="D350" s="7" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B351" s="6" t="inlineStr">
+        <is>
+          <t>Stream processing</t>
+        </is>
+      </c>
+      <c r="C351" s="5" t="n"/>
+      <c r="D351" s="5" t="n"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B352" s="8" t="inlineStr">
+        <is>
+          <t>Iterator design</t>
+        </is>
+      </c>
+      <c r="C352" s="7" t="n"/>
+      <c r="D352" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="A312:D312"/>
+    <mergeCell ref="A263:D263"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A159:D159"/>
+    <mergeCell ref="A234:D234"/>
+    <mergeCell ref="A206:D206"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="A324:D324"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A127:D127"/>
+    <mergeCell ref="A186:D186"/>
+    <mergeCell ref="A107:D107"/>
+    <mergeCell ref="A178:D178"/>
+    <mergeCell ref="A291:D291"/>
+    <mergeCell ref="A138:D138"/>
+    <mergeCell ref="A225:D225"/>
+    <mergeCell ref="A334:D334"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A343:D343"/>
+    <mergeCell ref="A168:D168"/>
+    <mergeCell ref="A196:D196"/>
+    <mergeCell ref="A243:D243"/>
+    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A282:D282"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A149:D149"/>
+    <mergeCell ref="A214:D214"/>
+    <mergeCell ref="A272:D272"/>
+    <mergeCell ref="A302:D302"/>
+    <mergeCell ref="A95:J95"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A254:D254"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C10:C35">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
+      <formula>"4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
+      <formula>"3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="between" dxfId="2">
+      <formula>"1"</formula>
+      <formula>"2"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H10:H35">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="0">
+      <formula>"5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
+      <formula>"4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+      <formula>"3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="between" dxfId="2">
+      <formula>"1"</formula>
+      <formula>"2"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G39:G64">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="0">
+      <formula>"Interview Ready"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="1">
+      <formula>"Needs Revision"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B68:B93">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
+      <formula>"Done"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="1">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="2">
+      <formula>"Not Started"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C68:C93">
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="0">
+      <formula>"Done"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="1">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="16" operator="equal" dxfId="2">
+      <formula>"Not Started"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D68:D93">
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="0">
+      <formula>"Done"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="1">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="2">
+      <formula>"Not Started"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E68:E93">
+    <cfRule type="cellIs" priority="20" operator="equal" dxfId="0">
+      <formula>"Done"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="21" operator="equal" dxfId="1">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="22" operator="equal" dxfId="2">
+      <formula>"Not Started"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C98:C105">
+    <cfRule type="cellIs" priority="23" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="24" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="25" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C109:C115">
+    <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="27" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="28" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C119:C125">
+    <cfRule type="cellIs" priority="29" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="30" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="31" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C129:C136">
+    <cfRule type="cellIs" priority="32" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="33" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="34" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C140:C147">
+    <cfRule type="cellIs" priority="35" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="36" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="37" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C151:C157">
+    <cfRule type="cellIs" priority="38" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="39" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="40" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C161:C166">
+    <cfRule type="cellIs" priority="41" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="42" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="43" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C170:C176">
+    <cfRule type="cellIs" priority="44" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="45" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="46" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C180:C184">
+    <cfRule type="cellIs" priority="47" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="48" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="49" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C188:C194">
+    <cfRule type="cellIs" priority="50" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="51" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="52" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C198:C204">
+    <cfRule type="cellIs" priority="53" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="54" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="55" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C208:C212">
+    <cfRule type="cellIs" priority="56" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="57" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="58" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C216:C223">
+    <cfRule type="cellIs" priority="59" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="60" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="61" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C227:C232">
+    <cfRule type="cellIs" priority="62" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="63" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="64" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C236:C241">
+    <cfRule type="cellIs" priority="65" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="66" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="67" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C245:C252">
+    <cfRule type="cellIs" priority="68" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="69" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="70" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C256:C261">
+    <cfRule type="cellIs" priority="71" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="72" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="73" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C265:C270">
+    <cfRule type="cellIs" priority="74" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="75" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="76" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C274:C280">
+    <cfRule type="cellIs" priority="77" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="78" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="79" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C284:C289">
+    <cfRule type="cellIs" priority="80" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="81" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="82" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C293:C300">
+    <cfRule type="cellIs" priority="83" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="84" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="85" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C304:C310">
+    <cfRule type="cellIs" priority="86" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="87" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="88" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C314:C322">
+    <cfRule type="cellIs" priority="89" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="90" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="91" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C326:C332">
+    <cfRule type="cellIs" priority="92" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="93" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="94" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C336:C341">
+    <cfRule type="cellIs" priority="95" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="96" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="97" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C345:C352">
+    <cfRule type="cellIs" priority="98" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="99" operator="equal" dxfId="1">
+      <formula>"Partially"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="100" operator="equal" dxfId="2">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="36">
+    <dataValidation sqref="C10:C35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1,2,3,4,5"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D10:D35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E10:E35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F10:F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G10:G35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H10:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1,2,3,4,5"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B68:B93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Done,In Progress,Not Started"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C68:C93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Done,In Progress,Not Started"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D68:D93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Done,In Progress,Not Started"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E68:E93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Done,In Progress,Not Started"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C98:C105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C109:C115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C119:C125" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C129:C136" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C140:C147" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C151:C157" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C161:C166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C170:C176" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C180:C184" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C188:C194" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C198:C204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C208:C212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C216:C223" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C227:C232" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C236:C241" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C245:C252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C256:C261" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C265:C270" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C274:C280" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C284:C289" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C293:C300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C304:C310" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C314:C322" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C326:C332" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C336:C341" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C345:C352" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,Partially,No"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00F472B6"/>
@@ -13201,7 +19317,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00FB923C"/>
@@ -13915,7 +20031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0060A5FA"/>
@@ -14473,7 +20589,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00F87171"/>
@@ -15021,7 +21137,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0034D399"/>
@@ -15627,7 +21743,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0022D3EE"/>
@@ -19320,7 +25436,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A78BFA"/>
@@ -20329,703 +26445,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00FB923C"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="32" customWidth="1" min="16" max="16"/>
-    <col width="32" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Pattern</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Solved?</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>Pattern</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>Solved?</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="O1" s="4" t="inlineStr">
-        <is>
-          <t>Score(1-10)</t>
-        </is>
-      </c>
-      <c r="P1" s="4" t="inlineStr">
-        <is>
-          <t>Mistakes</t>
-        </is>
-      </c>
-      <c r="Q1" s="4" t="inlineStr">
-        <is>
-          <t>Lessons</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="n"/>
-      <c r="B2" s="6" t="n"/>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
-      <c r="P2" s="5" t="n"/>
-      <c r="Q2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="7" t="n"/>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="n"/>
-      <c r="I3" s="7" t="n"/>
-      <c r="J3" s="7" t="n"/>
-      <c r="K3" s="7" t="n"/>
-      <c r="L3" s="7" t="n"/>
-      <c r="M3" s="7" t="n"/>
-      <c r="N3" s="7" t="n"/>
-      <c r="O3" s="7" t="n"/>
-      <c r="P3" s="7" t="n"/>
-      <c r="Q3" s="7" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="n"/>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-      <c r="P4" s="5" t="n"/>
-      <c r="Q4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
-      <c r="K5" s="7" t="n"/>
-      <c r="L5" s="7" t="n"/>
-      <c r="M5" s="7" t="n"/>
-      <c r="N5" s="7" t="n"/>
-      <c r="O5" s="7" t="n"/>
-      <c r="P5" s="7" t="n"/>
-      <c r="Q5" s="7" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
-      <c r="K7" s="7" t="n"/>
-      <c r="L7" s="7" t="n"/>
-      <c r="M7" s="7" t="n"/>
-      <c r="N7" s="7" t="n"/>
-      <c r="O7" s="7" t="n"/>
-      <c r="P7" s="7" t="n"/>
-      <c r="Q7" s="7" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="7" t="n"/>
-      <c r="K9" s="7" t="n"/>
-      <c r="L9" s="7" t="n"/>
-      <c r="M9" s="7" t="n"/>
-      <c r="N9" s="7" t="n"/>
-      <c r="O9" s="7" t="n"/>
-      <c r="P9" s="7" t="n"/>
-      <c r="Q9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-      <c r="P10" s="5" t="n"/>
-      <c r="Q10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
-      <c r="N11" s="7" t="n"/>
-      <c r="O11" s="7" t="n"/>
-      <c r="P11" s="7" t="n"/>
-      <c r="Q11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-      <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="n"/>
-      <c r="O13" s="7" t="n"/>
-      <c r="P13" s="7" t="n"/>
-      <c r="Q13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="n"/>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-      <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="7" t="n"/>
-      <c r="N15" s="7" t="n"/>
-      <c r="O15" s="7" t="n"/>
-      <c r="P15" s="7" t="n"/>
-      <c r="Q15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="n"/>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-      <c r="P16" s="5" t="n"/>
-      <c r="Q16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="7" t="n"/>
-      <c r="K17" s="7" t="n"/>
-      <c r="L17" s="7" t="n"/>
-      <c r="M17" s="7" t="n"/>
-      <c r="N17" s="7" t="n"/>
-      <c r="O17" s="7" t="n"/>
-      <c r="P17" s="7" t="n"/>
-      <c r="Q17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="n"/>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-      <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
-      <c r="K19" s="7" t="n"/>
-      <c r="L19" s="7" t="n"/>
-      <c r="M19" s="7" t="n"/>
-      <c r="N19" s="7" t="n"/>
-      <c r="O19" s="7" t="n"/>
-      <c r="P19" s="7" t="n"/>
-      <c r="Q19" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-      <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="7" t="n"/>
-      <c r="J21" s="7" t="n"/>
-      <c r="K21" s="7" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="7" t="n"/>
-      <c r="N21" s="7" t="n"/>
-      <c r="O21" s="7" t="n"/>
-      <c r="P21" s="7" t="n"/>
-      <c r="Q21" s="7" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="n"/>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="7" t="n"/>
-      <c r="J23" s="7" t="n"/>
-      <c r="K23" s="7" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="7" t="n"/>
-      <c r="N23" s="7" t="n"/>
-      <c r="O23" s="7" t="n"/>
-      <c r="P23" s="7" t="n"/>
-      <c r="Q23" s="7" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="n"/>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-      <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="5" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="n"/>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
-      <c r="I25" s="7" t="n"/>
-      <c r="J25" s="7" t="n"/>
-      <c r="K25" s="7" t="n"/>
-      <c r="L25" s="7" t="n"/>
-      <c r="M25" s="7" t="n"/>
-      <c r="N25" s="7" t="n"/>
-      <c r="O25" s="7" t="n"/>
-      <c r="P25" s="7" t="n"/>
-      <c r="Q25" s="7" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="n"/>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-      <c r="P26" s="5" t="n"/>
-      <c r="Q26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="7" t="n"/>
-      <c r="J27" s="7" t="n"/>
-      <c r="K27" s="7" t="n"/>
-      <c r="L27" s="7" t="n"/>
-      <c r="M27" s="7" t="n"/>
-      <c r="N27" s="7" t="n"/>
-      <c r="O27" s="7" t="n"/>
-      <c r="P27" s="7" t="n"/>
-      <c r="Q27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="n"/>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="n"/>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="5" t="n"/>
-      <c r="P28" s="5" t="n"/>
-      <c r="Q28" s="5" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="7" t="n"/>
-      <c r="I29" s="7" t="n"/>
-      <c r="J29" s="7" t="n"/>
-      <c r="K29" s="7" t="n"/>
-      <c r="L29" s="7" t="n"/>
-      <c r="M29" s="7" t="n"/>
-      <c r="N29" s="7" t="n"/>
-      <c r="O29" s="7" t="n"/>
-      <c r="P29" s="7" t="n"/>
-      <c r="Q29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="n"/>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
-      <c r="P30" s="5" t="n"/>
-      <c r="Q30" s="5" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="7" t="n"/>
-      <c r="J31" s="7" t="n"/>
-      <c r="K31" s="7" t="n"/>
-      <c r="L31" s="7" t="n"/>
-      <c r="M31" s="7" t="n"/>
-      <c r="N31" s="7" t="n"/>
-      <c r="O31" s="7" t="n"/>
-      <c r="P31" s="7" t="n"/>
-      <c r="Q31" s="7" t="n"/>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="B2:B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Timed Solo,Peer Mock,Platform,Company Prep,System Design Mock"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C2:C31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"LeetCode,Pramp,Interviewing.io,Peer,Self,Hello Interview"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Interview-Preparation-Tracker.xlsx
+++ b/Interview-Preparation-Tracker.xlsx
@@ -31,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,6 +126,11 @@
       <color rgb="00FBBF24"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="0022D3EE"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -160,7 +165,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -215,11 +220,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="002D3748"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="002D3748"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -306,6 +322,13 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6931,7 +6954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J352"/>
+  <dimension ref="A1:K352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6942,8 +6965,9 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="38" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7012,6 +7036,7 @@
         <f>IF(COUNTA(H10:H35)&gt;0,ROUND(AVERAGE(H10:H35),1),"—")</f>
         <v/>
       </c>
+      <c r="K5" s="32" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="27" t="inlineStr">
@@ -7045,6 +7070,7 @@
       </c>
       <c r="I6" s="28" t="n"/>
       <c r="J6" s="28" t="n"/>
+      <c r="K6" s="28" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
@@ -7061,7 +7087,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Problems Solved</t>
+          <t>Mastered / Total</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -7102,6 +7128,11 @@
       <c r="J9" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Representative Problems</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7142,11 @@
           <t>Arrays &amp; Hashing</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>— / 7</t>
+        </is>
+      </c>
       <c r="C10" s="5" t="n"/>
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
@@ -7120,6 +7155,11 @@
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
+      <c r="K10" s="33" t="inlineStr">
+        <is>
+          <t>LC 1, 49, 238, 128, 347, 48, 54</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -7127,7 +7167,11 @@
           <t>Prefix Sum</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n"/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
@@ -7136,6 +7180,11 @@
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
       <c r="J11" s="7" t="n"/>
+      <c r="K11" s="34" t="inlineStr">
+        <is>
+          <t>LC 303, 560, 974, 1314</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7143,7 +7192,11 @@
           <t>Two Pointers</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>— / 5</t>
+        </is>
+      </c>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
@@ -7152,6 +7205,11 @@
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
+      <c r="K12" s="33" t="inlineStr">
+        <is>
+          <t>LC 11, 15, 75, 287, 5</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -7159,7 +7217,11 @@
           <t>Sliding Window</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>— / 11</t>
+        </is>
+      </c>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
@@ -7168,6 +7230,11 @@
       <c r="H13" s="7" t="n"/>
       <c r="I13" s="7" t="n"/>
       <c r="J13" s="7" t="n"/>
+      <c r="K13" s="34" t="inlineStr">
+        <is>
+          <t>LC 3, 76, 424, 438, 567, 239, 121</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -7175,7 +7242,11 @@
           <t>Binary Search</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>— / 10</t>
+        </is>
+      </c>
       <c r="C14" s="5" t="n"/>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
@@ -7184,6 +7255,11 @@
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
+      <c r="K14" s="33" t="inlineStr">
+        <is>
+          <t>LC 33, 875, 410, 4, 34, 153, 378</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -7191,7 +7267,11 @@
           <t>Bit Manipulation</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>— / 4</t>
+        </is>
+      </c>
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="7" t="n"/>
       <c r="E15" s="7" t="n"/>
@@ -7200,6 +7280,11 @@
       <c r="H15" s="7" t="n"/>
       <c r="I15" s="7" t="n"/>
       <c r="J15" s="7" t="n"/>
+      <c r="K15" s="34" t="inlineStr">
+        <is>
+          <t>LC 136, 191, 338, 371</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -7207,7 +7292,11 @@
           <t>Stack</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>— / 8</t>
+        </is>
+      </c>
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
@@ -7216,6 +7305,11 @@
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
+      <c r="K16" s="33" t="inlineStr">
+        <is>
+          <t>LC 739, 84, 42, 394, 402, 907</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -7223,7 +7317,11 @@
           <t>Monotonic Stack</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n"/>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
@@ -7232,6 +7330,11 @@
       <c r="H17" s="7" t="n"/>
       <c r="I17" s="7" t="n"/>
       <c r="J17" s="7" t="n"/>
+      <c r="K17" s="34" t="inlineStr">
+        <is>
+          <t>LC 739, 84, 503, 907, 901</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -7239,7 +7342,11 @@
           <t>Queue</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="5" t="n"/>
@@ -7248,6 +7355,11 @@
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
+      <c r="K18" s="33" t="inlineStr">
+        <is>
+          <t>LC 239, 622, 346</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -7255,7 +7367,11 @@
           <t>Heap / Priority Queue</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n"/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>— / 7</t>
+        </is>
+      </c>
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
@@ -7264,6 +7380,11 @@
       <c r="H19" s="7" t="n"/>
       <c r="I19" s="7" t="n"/>
       <c r="J19" s="7" t="n"/>
+      <c r="K19" s="34" t="inlineStr">
+        <is>
+          <t>LC 215, 295, 253, 23, 632, 973</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -7271,7 +7392,11 @@
           <t>Linked List</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>— / 7</t>
+        </is>
+      </c>
       <c r="C20" s="5" t="n"/>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
@@ -7280,6 +7405,11 @@
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="5" t="n"/>
       <c r="J20" s="5" t="n"/>
+      <c r="K20" s="33" t="inlineStr">
+        <is>
+          <t>LC 206, 141, 19, 2, 25, 143, 138</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -7287,7 +7417,11 @@
           <t>Fast &amp; Slow Pointer</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n"/>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="C21" s="7" t="n"/>
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
@@ -7296,6 +7430,11 @@
       <c r="H21" s="7" t="n"/>
       <c r="I21" s="7" t="n"/>
       <c r="J21" s="7" t="n"/>
+      <c r="K21" s="34" t="inlineStr">
+        <is>
+          <t>LC 141, 142, 287, 876, 202</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -7303,7 +7442,11 @@
           <t>Trees (DFS)</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>— / 15</t>
+        </is>
+      </c>
       <c r="C22" s="5" t="n"/>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
@@ -7312,6 +7455,11 @@
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="5" t="n"/>
       <c r="J22" s="5" t="n"/>
+      <c r="K22" s="33" t="inlineStr">
+        <is>
+          <t>LC 124, 543, 297, 236, 105, 114</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -7319,7 +7467,11 @@
           <t>Trees (BFS)</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n"/>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="C23" s="7" t="n"/>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
@@ -7328,6 +7480,11 @@
       <c r="H23" s="7" t="n"/>
       <c r="I23" s="7" t="n"/>
       <c r="J23" s="7" t="n"/>
+      <c r="K23" s="34" t="inlineStr">
+        <is>
+          <t>LC 102, 199, 863, 637</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -7335,7 +7492,11 @@
           <t>Binary Search Tree</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="C24" s="5" t="n"/>
       <c r="D24" s="5" t="n"/>
       <c r="E24" s="5" t="n"/>
@@ -7344,6 +7505,11 @@
       <c r="H24" s="5" t="n"/>
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
+      <c r="K24" s="33" t="inlineStr">
+        <is>
+          <t>LC 98, 230, 235, 701</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -7351,7 +7517,11 @@
           <t>Graph DFS</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n"/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>— / 20</t>
+        </is>
+      </c>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
@@ -7360,6 +7530,11 @@
       <c r="H25" s="7" t="n"/>
       <c r="I25" s="7" t="n"/>
       <c r="J25" s="7" t="n"/>
+      <c r="K25" s="34" t="inlineStr">
+        <is>
+          <t>LC 200, 695, 417, 207, 133, 802</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -7367,7 +7542,11 @@
           <t>Graph BFS</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="C26" s="5" t="n"/>
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="n"/>
@@ -7376,6 +7555,11 @@
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="5" t="n"/>
       <c r="J26" s="5" t="n"/>
+      <c r="K26" s="33" t="inlineStr">
+        <is>
+          <t>LC 994, 127, 286, 1091</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -7383,7 +7567,11 @@
           <t>Topological Sort</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n"/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
@@ -7392,6 +7580,11 @@
       <c r="H27" s="7" t="n"/>
       <c r="I27" s="7" t="n"/>
       <c r="J27" s="7" t="n"/>
+      <c r="K27" s="34" t="inlineStr">
+        <is>
+          <t>LC 207, 210, 269, 2115</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -7399,7 +7592,11 @@
           <t>Union Find (Disjoint Set)</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n"/>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="C28" s="5" t="n"/>
       <c r="D28" s="5" t="n"/>
       <c r="E28" s="5" t="n"/>
@@ -7408,6 +7605,11 @@
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="n"/>
       <c r="J28" s="5" t="n"/>
+      <c r="K28" s="33" t="inlineStr">
+        <is>
+          <t>LC 547, 684, 721, 323, 1584</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -7415,7 +7617,11 @@
           <t>Trie</t>
         </is>
       </c>
-      <c r="B29" s="7" t="n"/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="C29" s="7" t="n"/>
       <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
@@ -7424,6 +7630,11 @@
       <c r="H29" s="7" t="n"/>
       <c r="I29" s="7" t="n"/>
       <c r="J29" s="7" t="n"/>
+      <c r="K29" s="34" t="inlineStr">
+        <is>
+          <t>LC 208, 211, 212, 642</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -7431,7 +7642,11 @@
           <t>Backtracking</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n"/>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>— / 6</t>
+        </is>
+      </c>
       <c r="C30" s="5" t="n"/>
       <c r="D30" s="5" t="n"/>
       <c r="E30" s="5" t="n"/>
@@ -7440,6 +7655,11 @@
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="n"/>
       <c r="J30" s="5" t="n"/>
+      <c r="K30" s="33" t="inlineStr">
+        <is>
+          <t>LC 39, 46, 78, 79, 22, 51</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -7447,7 +7667,11 @@
           <t>Greedy</t>
         </is>
       </c>
-      <c r="B31" s="7" t="n"/>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>— / 5</t>
+        </is>
+      </c>
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
@@ -7456,6 +7680,11 @@
       <c r="H31" s="7" t="n"/>
       <c r="I31" s="7" t="n"/>
       <c r="J31" s="7" t="n"/>
+      <c r="K31" s="34" t="inlineStr">
+        <is>
+          <t>LC 55, 45, 53, 621, 134</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -7463,7 +7692,11 @@
           <t>Dynamic Programming</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n"/>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>— / 22</t>
+        </is>
+      </c>
       <c r="C32" s="5" t="n"/>
       <c r="D32" s="5" t="n"/>
       <c r="E32" s="5" t="n"/>
@@ -7472,6 +7705,11 @@
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="5" t="n"/>
       <c r="J32" s="5" t="n"/>
+      <c r="K32" s="33" t="inlineStr">
+        <is>
+          <t>LC 322, 72, 300, 1143, 198, 312, 152, 329</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -7479,7 +7717,11 @@
           <t>Interval Problems</t>
         </is>
       </c>
-      <c r="B33" s="7" t="n"/>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>— / 4</t>
+        </is>
+      </c>
       <c r="C33" s="7" t="n"/>
       <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
@@ -7488,6 +7730,11 @@
       <c r="H33" s="7" t="n"/>
       <c r="I33" s="7" t="n"/>
       <c r="J33" s="7" t="n"/>
+      <c r="K33" s="34" t="inlineStr">
+        <is>
+          <t>LC 56, 57, 435, 252, 253</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -7495,7 +7742,11 @@
           <t>Matrix Problems</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n"/>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="C34" s="5" t="n"/>
       <c r="D34" s="5" t="n"/>
       <c r="E34" s="5" t="n"/>
@@ -7504,6 +7755,11 @@
       <c r="H34" s="5" t="n"/>
       <c r="I34" s="5" t="n"/>
       <c r="J34" s="5" t="n"/>
+      <c r="K34" s="33" t="inlineStr">
+        <is>
+          <t>LC 48, 54, 73, 74</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -7511,7 +7767,11 @@
           <t>Design Problems</t>
         </is>
       </c>
-      <c r="B35" s="7" t="n"/>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>— / 11</t>
+        </is>
+      </c>
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
@@ -7520,6 +7780,11 @@
       <c r="H35" s="7" t="n"/>
       <c r="I35" s="7" t="n"/>
       <c r="J35" s="7" t="n"/>
+      <c r="K35" s="34" t="inlineStr">
+        <is>
+          <t>LC 146, 460, 208, 380, 981, 706, 642, 212</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="23" t="inlineStr">
@@ -11694,39 +11959,39 @@
   <mergeCells count="36">
     <mergeCell ref="A312:D312"/>
     <mergeCell ref="A263:D263"/>
-    <mergeCell ref="A8:J8"/>
     <mergeCell ref="A159:D159"/>
     <mergeCell ref="A234:D234"/>
     <mergeCell ref="A206:D206"/>
     <mergeCell ref="A96:D96"/>
     <mergeCell ref="A324:D324"/>
-    <mergeCell ref="A4:J4"/>
     <mergeCell ref="A117:D117"/>
+    <mergeCell ref="A1:K1"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="A127:D127"/>
     <mergeCell ref="A186:D186"/>
+    <mergeCell ref="A66:K66"/>
     <mergeCell ref="A107:D107"/>
     <mergeCell ref="A178:D178"/>
     <mergeCell ref="A291:D291"/>
+    <mergeCell ref="A37:K37"/>
     <mergeCell ref="A138:D138"/>
     <mergeCell ref="A225:D225"/>
     <mergeCell ref="A334:D334"/>
-    <mergeCell ref="A1:J1"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="A343:D343"/>
     <mergeCell ref="A168:D168"/>
+    <mergeCell ref="A95:K95"/>
+    <mergeCell ref="A2:K2"/>
     <mergeCell ref="A196:D196"/>
     <mergeCell ref="A243:D243"/>
-    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A8:K8"/>
     <mergeCell ref="A282:D282"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A4:K4"/>
     <mergeCell ref="A149:D149"/>
     <mergeCell ref="A214:D214"/>
     <mergeCell ref="A272:D272"/>
     <mergeCell ref="A302:D302"/>
-    <mergeCell ref="A95:J95"/>
-    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A254:D254"/>
   </mergeCells>
   <conditionalFormatting sqref="C10:C35">

--- a/Interview-Preparation-Tracker.xlsx
+++ b/Interview-Preparation-Tracker.xlsx
@@ -165,7 +165,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -212,17 +212,6 @@
       <right style="thin">
         <color rgb="002D3748"/>
       </right>
-      <top style="thin">
-        <color rgb="002D3748"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="002D3748"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color rgb="002D3748"/>
       </top>
@@ -311,6 +300,7 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -318,17 +308,16 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -736,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -769,7 +758,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>TRACK ALLOCATION</t>
+          <t>PHASE 1: DSA-HEAVY (Months 1–4) — DSA is the gating round at Tier-1 companies</t>
         </is>
       </c>
     </row>
@@ -791,7 +780,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>Focus</t>
         </is>
       </c>
     </row>
@@ -803,24 +792,24 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>~4.5h</t>
+          <t>~6.75h</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>142 problems</t>
+          <t>142 problems — highest interview impact</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Java &amp; Backend</t>
+          <t>System Design + DDIA</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -835,29 +824,29 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>3 sub-tracks</t>
+          <t>DDIA Ch 1-6 + 3 HLD designs</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>System Design + DDIA</t>
+          <t>Java &amp; Backend</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>~3.75h</t>
+          <t>~2.25h</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>9 chapters + 8 designs</t>
+          <t>Effective Java + Design Patterns started</t>
         </is>
       </c>
     </row>
@@ -879,7 +868,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>11 + 5 topics</t>
+          <t>Kafka fundamentals + consumers</t>
         </is>
       </c>
     </row>
@@ -891,310 +880,449 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>~1.5h</t>
+          <t>~0.75h</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>5 technologies</t>
+          <t>Docker basics</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>MONTHLY MILESTONES</t>
+          <t>PHASE 2: BALANCED (Months 5–8) — After DSA patterns are solid</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>Track</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Hrs/Wk</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>DSA</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>~3h</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Revision + hard problems + mock interviews</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>System Design + DDIA</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>~4.5h</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>DDIA Ch 7-9 + 5 HLD designs + mocks</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Java &amp; Backend</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>~3.75h</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Design Patterns done + Spring Boot deep dive</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Kafka &amp; Redis</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>~2.25h</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Kafka reliability + Redis patterns</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Cloud &amp; Platform</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>~1.5h</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>K8s, OpenShift, CI/CD, AWS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>MONTHLY MILESTONES</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>DSA</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Java &amp; Backend</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>System Design</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Kafka/Redis</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Cloud/Platform</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Month 1</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Phase 1: Arrays, Two Pointers, SW</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Effective Java started</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>DDIA Ch 1-2</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Kafka fundamentals</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Docker basics</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Month 2</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Phase 1-2: BS, Stack, Heap</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Effective Java 50%</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>DDIA Ch 3-4</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>Kafka consumers</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>Docker multi-stage</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Month 3</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Phase 2: LL, Intervals</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Effective Java done</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>DDIA Ch 5 + URL Shortener</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Kafka reliability</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>K8s basics</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Month 4</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Phase 3: Trees</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>Design Patterns started</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>DDIA Ch 6 + Rate Limiter</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>Redis fundamentals</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>K8s probes/HPA</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Month 5</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Phase 3: Graphs</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Design Patterns 50%</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>DDIA Ch 7 + Notification Sys</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Redis locking</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>OpenShift basics</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Month 6</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Phase 4: DP</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Design Patterns done</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>DDIA Ch 8-9 + Inventory</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>Integration practice</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>CI/CD pipelines</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Month 7</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Phase 4-5: Greedy, BT, Design</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Spring Boot deep dive</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Payment Sys + Search</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>E2E design</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>AWS fundamentals</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Month 8</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>Review + Mocks</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Spring Security</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>Dist Cache + Review</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>Mock interviews</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>Mock interviews</t>
         </is>
@@ -7036,10 +7164,10 @@
         <f>IF(COUNTA(H10:H35)&gt;0,ROUND(AVERAGE(H10:H35),1),"—")</f>
         <v/>
       </c>
-      <c r="K5" s="32" t="n"/>
+      <c r="K5" s="27" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>Strongest Pattern</t>
         </is>
@@ -7048,8 +7176,8 @@
         <f>IF(COUNTA(H10:H35)&gt;0,INDEX(A10:A35,MATCH(MAX(H10:H35),H10:H35,0)),"—")</f>
         <v/>
       </c>
-      <c r="C6" s="28" t="n"/>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="C6" s="29" t="n"/>
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>Weakest Pattern</t>
         </is>
@@ -7058,19 +7186,19 @@
         <f>IF(COUNTA(H10:H35)&gt;0,INDEX(A10:A35,MATCH(MIN(H10:H35),H10:H35,0)),"—")</f>
         <v/>
       </c>
-      <c r="F6" s="28" t="n"/>
-      <c r="G6" s="27" t="inlineStr">
+      <c r="F6" s="29" t="n"/>
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t>Completion %</t>
         </is>
       </c>
-      <c r="H6" s="29">
+      <c r="H6" s="30">
         <f>IF(COUNTA(H10:H35)&gt;0,ROUND(COUNTIF(H10:H35,"&gt;=4")/26*100,0)&amp;"%","0%")</f>
         <v/>
       </c>
-      <c r="I6" s="28" t="n"/>
-      <c r="J6" s="28" t="n"/>
-      <c r="K6" s="28" t="n"/>
+      <c r="I6" s="29" t="n"/>
+      <c r="J6" s="29" t="n"/>
+      <c r="K6" s="29" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
@@ -7155,7 +7283,7 @@
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
-      <c r="K10" s="33" t="inlineStr">
+      <c r="K10" s="31" t="inlineStr">
         <is>
           <t>LC 1, 49, 238, 128, 347, 48, 54</t>
         </is>
@@ -7180,7 +7308,7 @@
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
       <c r="J11" s="7" t="n"/>
-      <c r="K11" s="34" t="inlineStr">
+      <c r="K11" s="32" t="inlineStr">
         <is>
           <t>LC 303, 560, 974, 1314</t>
         </is>
@@ -7205,7 +7333,7 @@
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
-      <c r="K12" s="33" t="inlineStr">
+      <c r="K12" s="31" t="inlineStr">
         <is>
           <t>LC 11, 15, 75, 287, 5</t>
         </is>
@@ -7230,7 +7358,7 @@
       <c r="H13" s="7" t="n"/>
       <c r="I13" s="7" t="n"/>
       <c r="J13" s="7" t="n"/>
-      <c r="K13" s="34" t="inlineStr">
+      <c r="K13" s="32" t="inlineStr">
         <is>
           <t>LC 3, 76, 424, 438, 567, 239, 121</t>
         </is>
@@ -7255,7 +7383,7 @@
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
-      <c r="K14" s="33" t="inlineStr">
+      <c r="K14" s="31" t="inlineStr">
         <is>
           <t>LC 33, 875, 410, 4, 34, 153, 378</t>
         </is>
@@ -7280,7 +7408,7 @@
       <c r="H15" s="7" t="n"/>
       <c r="I15" s="7" t="n"/>
       <c r="J15" s="7" t="n"/>
-      <c r="K15" s="34" t="inlineStr">
+      <c r="K15" s="32" t="inlineStr">
         <is>
           <t>LC 136, 191, 338, 371</t>
         </is>
@@ -7305,7 +7433,7 @@
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
-      <c r="K16" s="33" t="inlineStr">
+      <c r="K16" s="31" t="inlineStr">
         <is>
           <t>LC 739, 84, 42, 394, 402, 907</t>
         </is>
@@ -7330,7 +7458,7 @@
       <c r="H17" s="7" t="n"/>
       <c r="I17" s="7" t="n"/>
       <c r="J17" s="7" t="n"/>
-      <c r="K17" s="34" t="inlineStr">
+      <c r="K17" s="32" t="inlineStr">
         <is>
           <t>LC 739, 84, 503, 907, 901</t>
         </is>
@@ -7355,7 +7483,7 @@
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
-      <c r="K18" s="33" t="inlineStr">
+      <c r="K18" s="31" t="inlineStr">
         <is>
           <t>LC 239, 622, 346</t>
         </is>
@@ -7380,7 +7508,7 @@
       <c r="H19" s="7" t="n"/>
       <c r="I19" s="7" t="n"/>
       <c r="J19" s="7" t="n"/>
-      <c r="K19" s="34" t="inlineStr">
+      <c r="K19" s="32" t="inlineStr">
         <is>
           <t>LC 215, 295, 253, 23, 632, 973</t>
         </is>
@@ -7405,7 +7533,7 @@
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="5" t="n"/>
       <c r="J20" s="5" t="n"/>
-      <c r="K20" s="33" t="inlineStr">
+      <c r="K20" s="31" t="inlineStr">
         <is>
           <t>LC 206, 141, 19, 2, 25, 143, 138</t>
         </is>
@@ -7430,7 +7558,7 @@
       <c r="H21" s="7" t="n"/>
       <c r="I21" s="7" t="n"/>
       <c r="J21" s="7" t="n"/>
-      <c r="K21" s="34" t="inlineStr">
+      <c r="K21" s="32" t="inlineStr">
         <is>
           <t>LC 141, 142, 287, 876, 202</t>
         </is>
@@ -7455,7 +7583,7 @@
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="5" t="n"/>
       <c r="J22" s="5" t="n"/>
-      <c r="K22" s="33" t="inlineStr">
+      <c r="K22" s="31" t="inlineStr">
         <is>
           <t>LC 124, 543, 297, 236, 105, 114</t>
         </is>
@@ -7480,7 +7608,7 @@
       <c r="H23" s="7" t="n"/>
       <c r="I23" s="7" t="n"/>
       <c r="J23" s="7" t="n"/>
-      <c r="K23" s="34" t="inlineStr">
+      <c r="K23" s="32" t="inlineStr">
         <is>
           <t>LC 102, 199, 863, 637</t>
         </is>
@@ -7505,7 +7633,7 @@
       <c r="H24" s="5" t="n"/>
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
-      <c r="K24" s="33" t="inlineStr">
+      <c r="K24" s="31" t="inlineStr">
         <is>
           <t>LC 98, 230, 235, 701</t>
         </is>
@@ -7530,7 +7658,7 @@
       <c r="H25" s="7" t="n"/>
       <c r="I25" s="7" t="n"/>
       <c r="J25" s="7" t="n"/>
-      <c r="K25" s="34" t="inlineStr">
+      <c r="K25" s="32" t="inlineStr">
         <is>
           <t>LC 200, 695, 417, 207, 133, 802</t>
         </is>
@@ -7555,7 +7683,7 @@
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="5" t="n"/>
       <c r="J26" s="5" t="n"/>
-      <c r="K26" s="33" t="inlineStr">
+      <c r="K26" s="31" t="inlineStr">
         <is>
           <t>LC 994, 127, 286, 1091</t>
         </is>
@@ -7580,7 +7708,7 @@
       <c r="H27" s="7" t="n"/>
       <c r="I27" s="7" t="n"/>
       <c r="J27" s="7" t="n"/>
-      <c r="K27" s="34" t="inlineStr">
+      <c r="K27" s="32" t="inlineStr">
         <is>
           <t>LC 207, 210, 269, 2115</t>
         </is>
@@ -7605,7 +7733,7 @@
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="n"/>
       <c r="J28" s="5" t="n"/>
-      <c r="K28" s="33" t="inlineStr">
+      <c r="K28" s="31" t="inlineStr">
         <is>
           <t>LC 547, 684, 721, 323, 1584</t>
         </is>
@@ -7630,7 +7758,7 @@
       <c r="H29" s="7" t="n"/>
       <c r="I29" s="7" t="n"/>
       <c r="J29" s="7" t="n"/>
-      <c r="K29" s="34" t="inlineStr">
+      <c r="K29" s="32" t="inlineStr">
         <is>
           <t>LC 208, 211, 212, 642</t>
         </is>
@@ -7655,7 +7783,7 @@
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="n"/>
       <c r="J30" s="5" t="n"/>
-      <c r="K30" s="33" t="inlineStr">
+      <c r="K30" s="31" t="inlineStr">
         <is>
           <t>LC 39, 46, 78, 79, 22, 51</t>
         </is>
@@ -7680,7 +7808,7 @@
       <c r="H31" s="7" t="n"/>
       <c r="I31" s="7" t="n"/>
       <c r="J31" s="7" t="n"/>
-      <c r="K31" s="34" t="inlineStr">
+      <c r="K31" s="32" t="inlineStr">
         <is>
           <t>LC 55, 45, 53, 621, 134</t>
         </is>
@@ -7705,7 +7833,7 @@
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="5" t="n"/>
       <c r="J32" s="5" t="n"/>
-      <c r="K32" s="33" t="inlineStr">
+      <c r="K32" s="31" t="inlineStr">
         <is>
           <t>LC 322, 72, 300, 1143, 198, 312, 152, 329</t>
         </is>
@@ -7730,7 +7858,7 @@
       <c r="H33" s="7" t="n"/>
       <c r="I33" s="7" t="n"/>
       <c r="J33" s="7" t="n"/>
-      <c r="K33" s="34" t="inlineStr">
+      <c r="K33" s="32" t="inlineStr">
         <is>
           <t>LC 56, 57, 435, 252, 253</t>
         </is>
@@ -7755,7 +7883,7 @@
       <c r="H34" s="5" t="n"/>
       <c r="I34" s="5" t="n"/>
       <c r="J34" s="5" t="n"/>
-      <c r="K34" s="33" t="inlineStr">
+      <c r="K34" s="31" t="inlineStr">
         <is>
           <t>LC 48, 54, 73, 74</t>
         </is>
@@ -7780,7 +7908,7 @@
       <c r="H35" s="7" t="n"/>
       <c r="I35" s="7" t="n"/>
       <c r="J35" s="7" t="n"/>
-      <c r="K35" s="34" t="inlineStr">
+      <c r="K35" s="32" t="inlineStr">
         <is>
           <t>LC 146, 460, 208, 380, 981, 706, 642, 212</t>
         </is>
@@ -8964,14 +9092,14 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="30" t="inlineStr">
+      <c r="A96" s="33" t="inlineStr">
         <is>
           <t>Arrays &amp; Hashing</t>
         </is>
       </c>
-      <c r="B96" s="31" t="n"/>
-      <c r="C96" s="31" t="n"/>
-      <c r="D96" s="31" t="n"/>
+      <c r="B96" s="34" t="n"/>
+      <c r="C96" s="34" t="n"/>
+      <c r="D96" s="34" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -9092,14 +9220,14 @@
       <c r="D105" s="7" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="30" t="inlineStr">
+      <c r="A107" s="33" t="inlineStr">
         <is>
           <t>Prefix Sum</t>
         </is>
       </c>
-      <c r="B107" s="31" t="n"/>
-      <c r="C107" s="31" t="n"/>
-      <c r="D107" s="31" t="n"/>
+      <c r="B107" s="34" t="n"/>
+      <c r="C107" s="34" t="n"/>
+      <c r="D107" s="34" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -9208,14 +9336,14 @@
       <c r="D115" s="5" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="30" t="inlineStr">
+      <c r="A117" s="33" t="inlineStr">
         <is>
           <t>Two Pointers</t>
         </is>
       </c>
-      <c r="B117" s="31" t="n"/>
-      <c r="C117" s="31" t="n"/>
-      <c r="D117" s="31" t="n"/>
+      <c r="B117" s="34" t="n"/>
+      <c r="C117" s="34" t="n"/>
+      <c r="D117" s="34" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -9324,14 +9452,14 @@
       <c r="D125" s="5" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="30" t="inlineStr">
+      <c r="A127" s="33" t="inlineStr">
         <is>
           <t>Sliding Window</t>
         </is>
       </c>
-      <c r="B127" s="31" t="n"/>
-      <c r="C127" s="31" t="n"/>
-      <c r="D127" s="31" t="n"/>
+      <c r="B127" s="34" t="n"/>
+      <c r="C127" s="34" t="n"/>
+      <c r="D127" s="34" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -9452,14 +9580,14 @@
       <c r="D136" s="7" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="30" t="inlineStr">
+      <c r="A138" s="33" t="inlineStr">
         <is>
           <t>Binary Search</t>
         </is>
       </c>
-      <c r="B138" s="31" t="n"/>
-      <c r="C138" s="31" t="n"/>
-      <c r="D138" s="31" t="n"/>
+      <c r="B138" s="34" t="n"/>
+      <c r="C138" s="34" t="n"/>
+      <c r="D138" s="34" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -9580,14 +9708,14 @@
       <c r="D147" s="7" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="30" t="inlineStr">
+      <c r="A149" s="33" t="inlineStr">
         <is>
           <t>Bit Manipulation</t>
         </is>
       </c>
-      <c r="B149" s="31" t="n"/>
-      <c r="C149" s="31" t="n"/>
-      <c r="D149" s="31" t="n"/>
+      <c r="B149" s="34" t="n"/>
+      <c r="C149" s="34" t="n"/>
+      <c r="D149" s="34" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -9696,14 +9824,14 @@
       <c r="D157" s="5" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" s="30" t="inlineStr">
+      <c r="A159" s="33" t="inlineStr">
         <is>
           <t>Stack</t>
         </is>
       </c>
-      <c r="B159" s="31" t="n"/>
-      <c r="C159" s="31" t="n"/>
-      <c r="D159" s="31" t="n"/>
+      <c r="B159" s="34" t="n"/>
+      <c r="C159" s="34" t="n"/>
+      <c r="D159" s="34" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -9800,14 +9928,14 @@
       <c r="D166" s="7" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="30" t="inlineStr">
+      <c r="A168" s="33" t="inlineStr">
         <is>
           <t>Monotonic Stack</t>
         </is>
       </c>
-      <c r="B168" s="31" t="n"/>
-      <c r="C168" s="31" t="n"/>
-      <c r="D168" s="31" t="n"/>
+      <c r="B168" s="34" t="n"/>
+      <c r="C168" s="34" t="n"/>
+      <c r="D168" s="34" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -9916,14 +10044,14 @@
       <c r="D176" s="5" t="n"/>
     </row>
     <row r="178">
-      <c r="A178" s="30" t="inlineStr">
+      <c r="A178" s="33" t="inlineStr">
         <is>
           <t>Queue</t>
         </is>
       </c>
-      <c r="B178" s="31" t="n"/>
-      <c r="C178" s="31" t="n"/>
-      <c r="D178" s="31" t="n"/>
+      <c r="B178" s="34" t="n"/>
+      <c r="C178" s="34" t="n"/>
+      <c r="D178" s="34" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
@@ -10008,14 +10136,14 @@
       <c r="D184" s="5" t="n"/>
     </row>
     <row r="186">
-      <c r="A186" s="30" t="inlineStr">
+      <c r="A186" s="33" t="inlineStr">
         <is>
           <t>Heap / Priority Queue</t>
         </is>
       </c>
-      <c r="B186" s="31" t="n"/>
-      <c r="C186" s="31" t="n"/>
-      <c r="D186" s="31" t="n"/>
+      <c r="B186" s="34" t="n"/>
+      <c r="C186" s="34" t="n"/>
+      <c r="D186" s="34" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -10124,14 +10252,14 @@
       <c r="D194" s="5" t="n"/>
     </row>
     <row r="196">
-      <c r="A196" s="30" t="inlineStr">
+      <c r="A196" s="33" t="inlineStr">
         <is>
           <t>Linked List</t>
         </is>
       </c>
-      <c r="B196" s="31" t="n"/>
-      <c r="C196" s="31" t="n"/>
-      <c r="D196" s="31" t="n"/>
+      <c r="B196" s="34" t="n"/>
+      <c r="C196" s="34" t="n"/>
+      <c r="D196" s="34" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
@@ -10240,14 +10368,14 @@
       <c r="D204" s="5" t="n"/>
     </row>
     <row r="206">
-      <c r="A206" s="30" t="inlineStr">
+      <c r="A206" s="33" t="inlineStr">
         <is>
           <t>Fast &amp; Slow Pointer</t>
         </is>
       </c>
-      <c r="B206" s="31" t="n"/>
-      <c r="C206" s="31" t="n"/>
-      <c r="D206" s="31" t="n"/>
+      <c r="B206" s="34" t="n"/>
+      <c r="C206" s="34" t="n"/>
+      <c r="D206" s="34" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
@@ -10332,14 +10460,14 @@
       <c r="D212" s="5" t="n"/>
     </row>
     <row r="214">
-      <c r="A214" s="30" t="inlineStr">
+      <c r="A214" s="33" t="inlineStr">
         <is>
           <t>Trees (DFS)</t>
         </is>
       </c>
-      <c r="B214" s="31" t="n"/>
-      <c r="C214" s="31" t="n"/>
-      <c r="D214" s="31" t="n"/>
+      <c r="B214" s="34" t="n"/>
+      <c r="C214" s="34" t="n"/>
+      <c r="D214" s="34" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
@@ -10460,14 +10588,14 @@
       <c r="D223" s="7" t="n"/>
     </row>
     <row r="225">
-      <c r="A225" s="30" t="inlineStr">
+      <c r="A225" s="33" t="inlineStr">
         <is>
           <t>Trees (BFS)</t>
         </is>
       </c>
-      <c r="B225" s="31" t="n"/>
-      <c r="C225" s="31" t="n"/>
-      <c r="D225" s="31" t="n"/>
+      <c r="B225" s="34" t="n"/>
+      <c r="C225" s="34" t="n"/>
+      <c r="D225" s="34" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
@@ -10564,14 +10692,14 @@
       <c r="D232" s="7" t="n"/>
     </row>
     <row r="234">
-      <c r="A234" s="30" t="inlineStr">
+      <c r="A234" s="33" t="inlineStr">
         <is>
           <t>Binary Search Tree</t>
         </is>
       </c>
-      <c r="B234" s="31" t="n"/>
-      <c r="C234" s="31" t="n"/>
-      <c r="D234" s="31" t="n"/>
+      <c r="B234" s="34" t="n"/>
+      <c r="C234" s="34" t="n"/>
+      <c r="D234" s="34" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
@@ -10668,14 +10796,14 @@
       <c r="D241" s="7" t="n"/>
     </row>
     <row r="243">
-      <c r="A243" s="30" t="inlineStr">
+      <c r="A243" s="33" t="inlineStr">
         <is>
           <t>Graph DFS</t>
         </is>
       </c>
-      <c r="B243" s="31" t="n"/>
-      <c r="C243" s="31" t="n"/>
-      <c r="D243" s="31" t="n"/>
+      <c r="B243" s="34" t="n"/>
+      <c r="C243" s="34" t="n"/>
+      <c r="D243" s="34" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
@@ -10796,14 +10924,14 @@
       <c r="D252" s="7" t="n"/>
     </row>
     <row r="254">
-      <c r="A254" s="30" t="inlineStr">
+      <c r="A254" s="33" t="inlineStr">
         <is>
           <t>Graph BFS</t>
         </is>
       </c>
-      <c r="B254" s="31" t="n"/>
-      <c r="C254" s="31" t="n"/>
-      <c r="D254" s="31" t="n"/>
+      <c r="B254" s="34" t="n"/>
+      <c r="C254" s="34" t="n"/>
+      <c r="D254" s="34" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
@@ -10900,14 +11028,14 @@
       <c r="D261" s="7" t="n"/>
     </row>
     <row r="263">
-      <c r="A263" s="30" t="inlineStr">
+      <c r="A263" s="33" t="inlineStr">
         <is>
           <t>Topological Sort</t>
         </is>
       </c>
-      <c r="B263" s="31" t="n"/>
-      <c r="C263" s="31" t="n"/>
-      <c r="D263" s="31" t="n"/>
+      <c r="B263" s="34" t="n"/>
+      <c r="C263" s="34" t="n"/>
+      <c r="D263" s="34" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
@@ -11004,14 +11132,14 @@
       <c r="D270" s="7" t="n"/>
     </row>
     <row r="272">
-      <c r="A272" s="30" t="inlineStr">
+      <c r="A272" s="33" t="inlineStr">
         <is>
           <t>Union Find (Disjoint Set)</t>
         </is>
       </c>
-      <c r="B272" s="31" t="n"/>
-      <c r="C272" s="31" t="n"/>
-      <c r="D272" s="31" t="n"/>
+      <c r="B272" s="34" t="n"/>
+      <c r="C272" s="34" t="n"/>
+      <c r="D272" s="34" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
@@ -11120,14 +11248,14 @@
       <c r="D280" s="5" t="n"/>
     </row>
     <row r="282">
-      <c r="A282" s="30" t="inlineStr">
+      <c r="A282" s="33" t="inlineStr">
         <is>
           <t>Trie</t>
         </is>
       </c>
-      <c r="B282" s="31" t="n"/>
-      <c r="C282" s="31" t="n"/>
-      <c r="D282" s="31" t="n"/>
+      <c r="B282" s="34" t="n"/>
+      <c r="C282" s="34" t="n"/>
+      <c r="D282" s="34" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
@@ -11224,14 +11352,14 @@
       <c r="D289" s="7" t="n"/>
     </row>
     <row r="291">
-      <c r="A291" s="30" t="inlineStr">
+      <c r="A291" s="33" t="inlineStr">
         <is>
           <t>Backtracking</t>
         </is>
       </c>
-      <c r="B291" s="31" t="n"/>
-      <c r="C291" s="31" t="n"/>
-      <c r="D291" s="31" t="n"/>
+      <c r="B291" s="34" t="n"/>
+      <c r="C291" s="34" t="n"/>
+      <c r="D291" s="34" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
@@ -11352,14 +11480,14 @@
       <c r="D300" s="7" t="n"/>
     </row>
     <row r="302">
-      <c r="A302" s="30" t="inlineStr">
+      <c r="A302" s="33" t="inlineStr">
         <is>
           <t>Greedy</t>
         </is>
       </c>
-      <c r="B302" s="31" t="n"/>
-      <c r="C302" s="31" t="n"/>
-      <c r="D302" s="31" t="n"/>
+      <c r="B302" s="34" t="n"/>
+      <c r="C302" s="34" t="n"/>
+      <c r="D302" s="34" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
@@ -11468,14 +11596,14 @@
       <c r="D310" s="5" t="n"/>
     </row>
     <row r="312">
-      <c r="A312" s="30" t="inlineStr">
+      <c r="A312" s="33" t="inlineStr">
         <is>
           <t>Dynamic Programming</t>
         </is>
       </c>
-      <c r="B312" s="31" t="n"/>
-      <c r="C312" s="31" t="n"/>
-      <c r="D312" s="31" t="n"/>
+      <c r="B312" s="34" t="n"/>
+      <c r="C312" s="34" t="n"/>
+      <c r="D312" s="34" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
@@ -11608,14 +11736,14 @@
       <c r="D322" s="5" t="n"/>
     </row>
     <row r="324">
-      <c r="A324" s="30" t="inlineStr">
+      <c r="A324" s="33" t="inlineStr">
         <is>
           <t>Interval Problems</t>
         </is>
       </c>
-      <c r="B324" s="31" t="n"/>
-      <c r="C324" s="31" t="n"/>
-      <c r="D324" s="31" t="n"/>
+      <c r="B324" s="34" t="n"/>
+      <c r="C324" s="34" t="n"/>
+      <c r="D324" s="34" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
@@ -11724,14 +11852,14 @@
       <c r="D332" s="5" t="n"/>
     </row>
     <row r="334">
-      <c r="A334" s="30" t="inlineStr">
+      <c r="A334" s="33" t="inlineStr">
         <is>
           <t>Matrix Problems</t>
         </is>
       </c>
-      <c r="B334" s="31" t="n"/>
-      <c r="C334" s="31" t="n"/>
-      <c r="D334" s="31" t="n"/>
+      <c r="B334" s="34" t="n"/>
+      <c r="C334" s="34" t="n"/>
+      <c r="D334" s="34" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
@@ -11828,14 +11956,14 @@
       <c r="D341" s="7" t="n"/>
     </row>
     <row r="343">
-      <c r="A343" s="30" t="inlineStr">
+      <c r="A343" s="33" t="inlineStr">
         <is>
           <t>Design Problems</t>
         </is>
       </c>
-      <c r="B343" s="31" t="n"/>
-      <c r="C343" s="31" t="n"/>
-      <c r="D343" s="31" t="n"/>
+      <c r="B343" s="34" t="n"/>
+      <c r="C343" s="34" t="n"/>
+      <c r="D343" s="34" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
